--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -1117,45 +1117,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126811397</v>
+        <v>126814997</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>678330</v>
+        <v>678319</v>
       </c>
       <c r="R6" t="n">
-        <v>7105500</v>
+        <v>7105453</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,57 +1202,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126814997</v>
+        <v>126811397</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Råtjärnen, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>678319</v>
+        <v>678330</v>
       </c>
       <c r="R7" t="n">
-        <v>7105453</v>
+        <v>7105500</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,12 +1299,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126865187</v>
+        <v>126861260</v>
       </c>
       <c r="B19" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,34 +2417,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>678622</v>
+        <v>678449</v>
       </c>
       <c r="R19" t="n">
-        <v>7105605</v>
+        <v>7105699</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2488,30 +2488,15 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3046,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126861260</v>
+        <v>126865187</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3057,34 +3042,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>678449</v>
+        <v>678622</v>
       </c>
       <c r="R25" t="n">
-        <v>7105699</v>
+        <v>7105605</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,15 +3113,30 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -5644,45 +5644,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126861104</v>
+        <v>126865757</v>
       </c>
       <c r="B50" t="n">
-        <v>80021</v>
+        <v>78772</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>678269</v>
+        <v>678290</v>
       </c>
       <c r="R50" t="n">
-        <v>7105603</v>
+        <v>7105528</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5723,18 +5726,19 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5745,48 +5749,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126865757</v>
+        <v>126861104</v>
       </c>
       <c r="B51" t="n">
-        <v>78772</v>
+        <v>80021</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>678290</v>
+        <v>678269</v>
       </c>
       <c r="R51" t="n">
-        <v>7105528</v>
+        <v>7105603</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5827,19 +5828,18 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -9896,10 +9896,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126853137</v>
+        <v>126868553</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9907,37 +9907,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>678510</v>
+        <v>678439</v>
       </c>
       <c r="R91" t="n">
-        <v>7105573</v>
+        <v>7105679</v>
       </c>
       <c r="S91" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9964,19 +9964,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9991,12 +9981,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10007,7 +9997,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126861265</v>
+        <v>126862292</v>
       </c>
       <c r="B92" t="n">
         <v>79014</v>
@@ -10038,17 +10028,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>678512</v>
+        <v>678338</v>
       </c>
       <c r="R92" t="n">
-        <v>7105771</v>
+        <v>7105482</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10092,61 +10082,57 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126863396</v>
+        <v>126861082</v>
       </c>
       <c r="B93" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>678396</v>
+        <v>678240</v>
       </c>
       <c r="R93" t="n">
-        <v>7105690</v>
+        <v>7105623</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10193,12 +10179,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10209,10 +10195,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126868553</v>
+        <v>126853137</v>
       </c>
       <c r="B94" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10220,37 +10206,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>678439</v>
+        <v>678510</v>
       </c>
       <c r="R94" t="n">
-        <v>7105679</v>
+        <v>7105573</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10277,9 +10263,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10294,12 +10290,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10310,7 +10306,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126862292</v>
+        <v>126861265</v>
       </c>
       <c r="B95" t="n">
         <v>79014</v>
@@ -10341,17 +10337,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>678338</v>
+        <v>678512</v>
       </c>
       <c r="R95" t="n">
-        <v>7105482</v>
+        <v>7105771</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10395,44 +10391,48 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
+          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126861082</v>
+        <v>126861172</v>
       </c>
       <c r="B96" t="n">
-        <v>80146</v>
+        <v>80117</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10442,10 +10442,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>678240</v>
+        <v>678290</v>
       </c>
       <c r="R96" t="n">
-        <v>7105623</v>
+        <v>7105503</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10508,7 +10508,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126861172</v>
+        <v>126865284</v>
       </c>
       <c r="B97" t="n">
         <v>80117</v>
@@ -10537,16 +10537,19 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>678290</v>
+        <v>678332</v>
       </c>
       <c r="R97" t="n">
-        <v>7105503</v>
+        <v>7105581</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10590,15 +10593,30 @@
       <c r="AG97" t="b">
         <v>0</v>
       </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10609,37 +10627,38 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126865284</v>
+        <v>126867967</v>
       </c>
       <c r="B98" t="n">
-        <v>80117</v>
+        <v>98359</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10647,10 +10666,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>678332</v>
+        <v>678532</v>
       </c>
       <c r="R98" t="n">
-        <v>7105581</v>
+        <v>7105782</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10691,33 +10710,19 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Lotta Ihse, Mattias Dalkvist, Anne Siivola, Malin Löfgren, Philipp Weiss, Carl Jansson, Peder Winding, Martin Axegård, Fredrik Wilde, Vilhelm Kroon, Cajsa Björkén, Hedda Bring</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10728,49 +10733,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126867967</v>
+        <v>126863396</v>
       </c>
       <c r="B99" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>678532</v>
+        <v>678396</v>
       </c>
       <c r="R99" t="n">
-        <v>7105782</v>
+        <v>7105690</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10811,19 +10812,18 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Mattias Dalkvist, Anne Siivola, Malin Löfgren, Philipp Weiss, Carl Jansson, Peder Winding, Martin Axegård, Fredrik Wilde, Vilhelm Kroon, Cajsa Björkén, Hedda Bring</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -13394,45 +13394,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126861079</v>
+        <v>126865184</v>
       </c>
       <c r="B125" t="n">
-        <v>80146</v>
+        <v>92808</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>678363</v>
+        <v>678549</v>
       </c>
       <c r="R125" t="n">
-        <v>7105711</v>
+        <v>7105535</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13476,15 +13476,30 @@
       <c r="AG125" t="b">
         <v>0</v>
       </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13495,45 +13510,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126865251</v>
+        <v>126868610</v>
       </c>
       <c r="B126" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>678319</v>
+        <v>678379</v>
       </c>
       <c r="R126" t="n">
-        <v>7105574</v>
+        <v>7105668</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13577,30 +13592,15 @@
       <c r="AG126" t="b">
         <v>0</v>
       </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13611,32 +13611,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126868618</v>
+        <v>126861263</v>
       </c>
       <c r="B127" t="n">
-        <v>80052</v>
+        <v>79014</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>678324</v>
+        <v>678535</v>
       </c>
       <c r="R127" t="n">
-        <v>7105582</v>
+        <v>7105767</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13696,12 +13696,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13712,32 +13712,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126861167</v>
+        <v>126861079</v>
       </c>
       <c r="B128" t="n">
-        <v>80117</v>
+        <v>80146</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13747,10 +13747,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>678298</v>
+        <v>678363</v>
       </c>
       <c r="R128" t="n">
-        <v>7105658</v>
+        <v>7105711</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13813,45 +13813,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126861263</v>
+        <v>126865251</v>
       </c>
       <c r="B129" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>678535</v>
+        <v>678319</v>
       </c>
       <c r="R129" t="n">
-        <v>7105767</v>
+        <v>7105574</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13895,15 +13895,30 @@
       <c r="AG129" t="b">
         <v>0</v>
       </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -13914,45 +13929,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126865184</v>
+        <v>126868618</v>
       </c>
       <c r="B130" t="n">
-        <v>92808</v>
+        <v>80052</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2079</v>
+        <v>6457</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>678549</v>
+        <v>678324</v>
       </c>
       <c r="R130" t="n">
-        <v>7105535</v>
+        <v>7105582</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13996,30 +14011,15 @@
       <c r="AG130" t="b">
         <v>0</v>
       </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14030,10 +14030,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126868610</v>
+        <v>126861167</v>
       </c>
       <c r="B131" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14041,21 +14041,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14065,10 +14065,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>678379</v>
+        <v>678298</v>
       </c>
       <c r="R131" t="n">
-        <v>7105668</v>
+        <v>7105658</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14115,12 +14115,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14848,32 +14848,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126861105</v>
+        <v>126868588</v>
       </c>
       <c r="B139" t="n">
-        <v>80021</v>
+        <v>80117</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14886,7 +14886,7 @@
         <v>678330</v>
       </c>
       <c r="R139" t="n">
-        <v>7105447</v>
+        <v>7105451</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14933,12 +14933,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -14949,48 +14949,48 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126862287</v>
+        <v>126868617</v>
       </c>
       <c r="B140" t="n">
-        <v>79014</v>
+        <v>80052</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>678359</v>
+        <v>678328</v>
       </c>
       <c r="R140" t="n">
-        <v>7105587</v>
+        <v>7105581</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15034,44 +15034,48 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY140" t="inlineStr"/>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126868588</v>
+        <v>126861105</v>
       </c>
       <c r="B141" t="n">
-        <v>80117</v>
+        <v>80021</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15084,7 +15088,7 @@
         <v>678330</v>
       </c>
       <c r="R141" t="n">
-        <v>7105451</v>
+        <v>7105447</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15131,12 +15135,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15147,48 +15151,48 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126868617</v>
+        <v>126862287</v>
       </c>
       <c r="B142" t="n">
-        <v>80052</v>
+        <v>79014</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>678328</v>
+        <v>678359</v>
       </c>
       <c r="R142" t="n">
-        <v>7105581</v>
+        <v>7105587</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15232,19 +15236,15 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY142" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15450,32 +15450,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126868627</v>
+        <v>126868607</v>
       </c>
       <c r="B145" t="n">
-        <v>79990</v>
+        <v>91343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>392</v>
+        <v>5432</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15485,10 +15485,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>678330</v>
+        <v>678439</v>
       </c>
       <c r="R145" t="n">
-        <v>7105453</v>
+        <v>7105681</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15551,48 +15551,48 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126861324</v>
+        <v>126862298</v>
       </c>
       <c r="B146" t="n">
-        <v>79014</v>
+        <v>98359</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>678264</v>
+        <v>678316</v>
       </c>
       <c r="R146" t="n">
-        <v>7105625</v>
+        <v>7105563</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15636,64 +15636,64 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY146" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126868596</v>
+        <v>126853557</v>
       </c>
       <c r="B147" t="n">
-        <v>78772</v>
+        <v>98442</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>678293</v>
+        <v>678466</v>
       </c>
       <c r="R147" t="n">
-        <v>7105493</v>
+        <v>7105581</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15720,9 +15720,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15737,12 +15747,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15753,48 +15763,48 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126851438</v>
+        <v>126868627</v>
       </c>
       <c r="B148" t="n">
-        <v>80117</v>
+        <v>79990</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>392</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>678352</v>
+        <v>678330</v>
       </c>
       <c r="R148" t="n">
-        <v>7105670</v>
+        <v>7105453</v>
       </c>
       <c r="S148" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15821,19 +15831,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>10:23</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15848,22 +15848,26 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr"/>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126865296</v>
+        <v>126861324</v>
       </c>
       <c r="B149" t="n">
-        <v>41361</v>
+        <v>79014</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15871,47 +15875,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>215713</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>678332</v>
+        <v>678264</v>
       </c>
       <c r="R149" t="n">
-        <v>7105461</v>
+        <v>7105625</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15958,12 +15949,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -15974,10 +15965,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126866154</v>
+        <v>126868596</v>
       </c>
       <c r="B150" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15985,37 +15976,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
         <v>678293</v>
       </c>
       <c r="R150" t="n">
-        <v>7105600</v>
+        <v>7105493</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16059,12 +16050,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -16075,10 +16066,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126868607</v>
+        <v>126851438</v>
       </c>
       <c r="B151" t="n">
-        <v>91343</v>
+        <v>80117</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16086,37 +16077,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>678439</v>
+        <v>678352</v>
       </c>
       <c r="R151" t="n">
-        <v>7105681</v>
+        <v>7105670</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16143,9 +16134,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16160,64 +16161,73 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126862298</v>
+        <v>126865296</v>
       </c>
       <c r="B152" t="n">
-        <v>98359</v>
+        <v>41361</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>219790</v>
+        <v>215713</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>678316</v>
+        <v>678332</v>
       </c>
       <c r="R152" t="n">
-        <v>7105563</v>
+        <v>7105461</v>
       </c>
       <c r="S152" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16261,64 +16271,64 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY152" t="inlineStr"/>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126853557</v>
+        <v>126866154</v>
       </c>
       <c r="B153" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>678466</v>
+        <v>678293</v>
       </c>
       <c r="R153" t="n">
-        <v>7105581</v>
+        <v>7105600</v>
       </c>
       <c r="S153" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16345,19 +16355,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>11:29</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16372,12 +16372,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -22409,32 +22409,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>126865855</v>
+        <v>126866024</v>
       </c>
       <c r="B212" t="n">
-        <v>91325</v>
+        <v>80145</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22447,10 +22447,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>678579</v>
+        <v>678594</v>
       </c>
       <c r="R212" t="n">
-        <v>7105578</v>
+        <v>7105682</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22514,32 +22514,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>126866024</v>
+        <v>126865855</v>
       </c>
       <c r="B213" t="n">
-        <v>80145</v>
+        <v>91325</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22552,10 +22552,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>678594</v>
+        <v>678579</v>
       </c>
       <c r="R213" t="n">
-        <v>7105682</v>
+        <v>7105578</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23479,32 +23479,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>126865446</v>
+        <v>126865454</v>
       </c>
       <c r="B222" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23514,10 +23514,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>678289</v>
+        <v>678384</v>
       </c>
       <c r="R222" t="n">
-        <v>7105512</v>
+        <v>7105660</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23550,11 +23550,6 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>1 ex</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23585,32 +23580,32 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>126865454</v>
+        <v>126865446</v>
       </c>
       <c r="B223" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23620,10 +23615,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>678384</v>
+        <v>678289</v>
       </c>
       <c r="R223" t="n">
-        <v>7105660</v>
+        <v>7105512</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23656,6 +23651,11 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD223" t="b">

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -1514,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814999</v>
+        <v>126815009</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>678379</v>
+        <v>678404</v>
       </c>
       <c r="R10" t="n">
-        <v>7105495</v>
+        <v>7105442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126815000</v>
+        <v>126814999</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>678391</v>
+        <v>678379</v>
       </c>
       <c r="R11" t="n">
-        <v>7105482</v>
+        <v>7105495</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126815009</v>
+        <v>126815000</v>
       </c>
       <c r="B12" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1719,21 +1719,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>678404</v>
+        <v>678391</v>
       </c>
       <c r="R12" t="n">
-        <v>7105442</v>
+        <v>7105482</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,51 +1902,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126814989</v>
+        <v>126814998</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Råtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>678347</v>
+        <v>678369</v>
       </c>
       <c r="R14" t="n">
         <v>7105493</v>
@@ -2008,7 +1999,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126814987</v>
+        <v>126814989</v>
       </c>
       <c r="B15" t="n">
         <v>98443</v>
@@ -2038,7 +2029,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2052,10 +2043,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>678345</v>
+        <v>678347</v>
       </c>
       <c r="R15" t="n">
-        <v>7105495</v>
+        <v>7105493</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,45 +2105,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126814998</v>
+        <v>126814987</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Råtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>678369</v>
+        <v>678345</v>
       </c>
       <c r="R16" t="n">
-        <v>7105493</v>
+        <v>7105495</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3455,32 +3455,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126862275</v>
+        <v>126865317</v>
       </c>
       <c r="B29" t="n">
-        <v>91487</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3490,13 +3490,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>678635</v>
+        <v>678346</v>
       </c>
       <c r="R29" t="n">
-        <v>7105683</v>
+        <v>7105480</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3540,19 +3540,23 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126865317</v>
+        <v>126861317</v>
       </c>
       <c r="B30" t="n">
         <v>79014</v>
@@ -3583,14 +3587,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>678346</v>
+        <v>678337</v>
       </c>
       <c r="R30" t="n">
-        <v>7105480</v>
+        <v>7105662</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3637,12 +3641,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3653,48 +3657,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126861317</v>
+        <v>126862275</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>91487</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>678337</v>
+        <v>678635</v>
       </c>
       <c r="R31" t="n">
-        <v>7105662</v>
+        <v>7105683</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3738,19 +3742,15 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4184,59 +4184,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126861190</v>
+        <v>126861174</v>
       </c>
       <c r="B36" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>678394</v>
+        <v>678325</v>
       </c>
       <c r="R36" t="n">
-        <v>7105687</v>
+        <v>7105453</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4299,10 +4285,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126865315</v>
+        <v>126861189</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4310,34 +4296,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>678348</v>
+        <v>678292</v>
       </c>
       <c r="R37" t="n">
-        <v>7105510</v>
+        <v>7105494</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4384,12 +4370,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4400,10 +4386,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126868575</v>
+        <v>126861168</v>
       </c>
       <c r="B38" t="n">
-        <v>75133</v>
+        <v>80117</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4411,21 +4397,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>310</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4435,10 +4421,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>678314</v>
+        <v>678283</v>
       </c>
       <c r="R38" t="n">
-        <v>7105563</v>
+        <v>7105656</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4485,12 +4471,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4501,10 +4487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126862248</v>
+        <v>126865003</v>
       </c>
       <c r="B39" t="n">
-        <v>91736</v>
+        <v>80146</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4512,37 +4498,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4217</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>678320</v>
+        <v>678319</v>
       </c>
       <c r="R39" t="n">
-        <v>7105489</v>
+        <v>7105555</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4580,50 +4569,51 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126861174</v>
+        <v>126868625</v>
       </c>
       <c r="B40" t="n">
-        <v>80117</v>
+        <v>80152</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4633,10 +4623,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>678325</v>
+        <v>678364</v>
       </c>
       <c r="R40" t="n">
-        <v>7105453</v>
+        <v>7105634</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4683,12 +4673,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4699,45 +4689,59 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126861189</v>
+        <v>126861190</v>
       </c>
       <c r="B41" t="n">
-        <v>78772</v>
+        <v>98443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>678292</v>
+        <v>678394</v>
       </c>
       <c r="R41" t="n">
-        <v>7105494</v>
+        <v>7105687</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4800,48 +4804,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126861168</v>
+        <v>126862248</v>
       </c>
       <c r="B42" t="n">
-        <v>80117</v>
+        <v>91736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>4217</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>678283</v>
+        <v>678320</v>
       </c>
       <c r="R42" t="n">
-        <v>7105656</v>
+        <v>7105489</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4885,64 +4889,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126865003</v>
+        <v>126865315</v>
       </c>
       <c r="B43" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>678319</v>
+        <v>678348</v>
       </c>
       <c r="R43" t="n">
-        <v>7105555</v>
+        <v>7105510</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,51 +4980,54 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126868625</v>
+        <v>126868575</v>
       </c>
       <c r="B44" t="n">
-        <v>80152</v>
+        <v>75133</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>678364</v>
+        <v>678314</v>
       </c>
       <c r="R44" t="n">
-        <v>7105634</v>
+        <v>7105563</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126865181</v>
+        <v>126865186</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>77992</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5114,21 +5114,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>678324</v>
+        <v>678622</v>
       </c>
       <c r="R45" t="n">
-        <v>7105598</v>
+        <v>7105605</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5187,17 +5187,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5219,7 +5219,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126862286</v>
+        <v>126865181</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5250,17 +5250,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>678452</v>
+        <v>678324</v>
       </c>
       <c r="R46" t="n">
-        <v>7105602</v>
+        <v>7105598</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5300,23 +5300,42 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126850977</v>
+        <v>126862286</v>
       </c>
       <c r="B47" t="n">
         <v>79014</v>
@@ -5347,17 +5366,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>678347</v>
+        <v>678452</v>
       </c>
       <c r="R47" t="n">
         <v>7105602</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5384,19 +5403,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5411,64 +5420,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126861104</v>
+        <v>126850977</v>
       </c>
       <c r="B48" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>678269</v>
+        <v>678347</v>
       </c>
       <c r="R48" t="n">
-        <v>7105603</v>
+        <v>7105602</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5495,9 +5500,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5512,12 +5527,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5528,48 +5543,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126865757</v>
+        <v>126861104</v>
       </c>
       <c r="B49" t="n">
-        <v>78772</v>
+        <v>80021</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>678290</v>
+        <v>678269</v>
       </c>
       <c r="R49" t="n">
-        <v>7105528</v>
+        <v>7105603</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5610,19 +5622,18 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5633,10 +5644,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126865186</v>
+        <v>126865757</v>
       </c>
       <c r="B50" t="n">
-        <v>77992</v>
+        <v>78772</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5644,34 +5655,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>678622</v>
+        <v>678290</v>
       </c>
       <c r="R50" t="n">
-        <v>7105605</v>
+        <v>7105528</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5712,33 +5726,19 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5749,10 +5749,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126861056</v>
+        <v>126865246</v>
       </c>
       <c r="B51" t="n">
-        <v>91326</v>
+        <v>57817</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5760,34 +5760,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>678315</v>
+        <v>678584</v>
       </c>
       <c r="R51" t="n">
-        <v>7105477</v>
+        <v>7105735</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5834,12 +5834,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5850,45 +5850,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126865246</v>
+        <v>126861122</v>
       </c>
       <c r="B52" t="n">
-        <v>57817</v>
+        <v>8447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>678584</v>
+        <v>678233</v>
       </c>
       <c r="R52" t="n">
-        <v>7105735</v>
+        <v>7105643</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5935,12 +5940,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5951,10 +5956,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126861122</v>
+        <v>126866161</v>
       </c>
       <c r="B53" t="n">
-        <v>8447</v>
+        <v>98360</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5962,42 +5967,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>678233</v>
+        <v>678315</v>
       </c>
       <c r="R53" t="n">
-        <v>7105643</v>
+        <v>7105536</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6041,12 +6041,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6057,32 +6057,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126866161</v>
+        <v>126862265</v>
       </c>
       <c r="B54" t="n">
-        <v>98360</v>
+        <v>78773</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6092,13 +6092,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>678315</v>
+        <v>678288</v>
       </c>
       <c r="R54" t="n">
-        <v>7105536</v>
+        <v>7105530</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6142,23 +6142,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126862265</v>
+        <v>126865464</v>
       </c>
       <c r="B55" t="n">
         <v>78773</v>
@@ -6187,19 +6183,22 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>678288</v>
+        <v>678496</v>
       </c>
       <c r="R55" t="n">
-        <v>7105530</v>
+        <v>7105543</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6237,28 +6236,29 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126865464</v>
+        <v>126861056</v>
       </c>
       <c r="B56" t="n">
-        <v>78773</v>
+        <v>91326</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6266,37 +6266,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>678496</v>
+        <v>678315</v>
       </c>
       <c r="R56" t="n">
-        <v>7105543</v>
+        <v>7105477</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6337,22 +6334,25 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7211,45 +7211,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126861053</v>
+        <v>126865314</v>
       </c>
       <c r="B65" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>678315</v>
+        <v>678506</v>
       </c>
       <c r="R65" t="n">
-        <v>7105477</v>
+        <v>7105716</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7296,12 +7296,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7312,10 +7312,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126868541</v>
+        <v>126864836</v>
       </c>
       <c r="B66" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7323,34 +7323,45 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>678322</v>
+        <v>678301</v>
       </c>
       <c r="R66" t="n">
-        <v>7105557</v>
+        <v>7105516</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7391,32 +7402,29 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126861165</v>
+        <v>126862290</v>
       </c>
       <c r="B67" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7424,37 +7432,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>678337</v>
+        <v>678323</v>
       </c>
       <c r="R67" t="n">
-        <v>7105669</v>
+        <v>7105490</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7498,64 +7506,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126861100</v>
+        <v>126862289</v>
       </c>
       <c r="B68" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>678335</v>
+        <v>678303</v>
       </c>
       <c r="R68" t="n">
-        <v>7105661</v>
+        <v>7105511</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7599,26 +7603,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126856160</v>
+        <v>126868541</v>
       </c>
       <c r="B69" t="n">
-        <v>78420</v>
+        <v>75138</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7626,37 +7626,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>678553</v>
+        <v>678322</v>
       </c>
       <c r="R69" t="n">
-        <v>7105588</v>
+        <v>7105557</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7683,19 +7683,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:32</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7710,12 +7700,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7726,7 +7716,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126860445</v>
+        <v>126861165</v>
       </c>
       <c r="B70" t="n">
         <v>80117</v>
@@ -7757,14 +7747,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>678290</v>
+        <v>678337</v>
       </c>
       <c r="R70" t="n">
-        <v>7105581</v>
+        <v>7105669</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7794,19 +7784,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>09:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7821,12 +7801,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7837,62 +7817,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126853937</v>
+        <v>126861100</v>
       </c>
       <c r="B71" t="n">
-        <v>98443</v>
+        <v>80021</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>678352</v>
+        <v>678335</v>
       </c>
       <c r="R71" t="n">
-        <v>7105670</v>
+        <v>7105661</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7919,19 +7885,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:39</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7946,64 +7902,64 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126868599</v>
+        <v>126856160</v>
       </c>
       <c r="B72" t="n">
-        <v>98443</v>
+        <v>78420</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>678290</v>
+        <v>678553</v>
       </c>
       <c r="R72" t="n">
-        <v>7105494</v>
+        <v>7105588</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8030,14 +7986,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Delvis blommande, grovt uppskattat antal</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8052,12 +8013,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8068,10 +8029,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126865754</v>
+        <v>126860445</v>
       </c>
       <c r="B73" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8079,37 +8040,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>678603</v>
+        <v>678290</v>
       </c>
       <c r="R73" t="n">
-        <v>7105660</v>
+        <v>7105581</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8139,30 +8097,39 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Mattias Dalkvist, Anne Siivola, Malin Löfgren, Philipp Weiss, Carl Jansson, Peder Winding, Martin Axegård, Fredrik Wilde, Vilhelm Kroon, Cajsa Björkén, Hedda Bring</t>
+          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8173,48 +8140,62 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126861113</v>
+        <v>126853937</v>
       </c>
       <c r="B74" t="n">
-        <v>97321</v>
+        <v>98443</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>678242</v>
+        <v>678352</v>
       </c>
       <c r="R74" t="n">
-        <v>7105626</v>
+        <v>7105670</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8241,9 +8222,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8258,61 +8249,61 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126865314</v>
+        <v>126868599</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>678506</v>
+        <v>678290</v>
       </c>
       <c r="R75" t="n">
-        <v>7105716</v>
+        <v>7105494</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8347,6 +8338,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Delvis blommande, grovt uppskattat antal</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8359,12 +8355,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8375,10 +8371,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126864836</v>
+        <v>126865754</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8386,33 +8382,25 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -8421,10 +8409,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>678301</v>
+        <v>678603</v>
       </c>
       <c r="R76" t="n">
-        <v>7105516</v>
+        <v>7105660</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8472,60 +8460,64 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Lotta Ihse, Mattias Dalkvist, Anne Siivola, Malin Löfgren, Philipp Weiss, Carl Jansson, Peder Winding, Martin Axegård, Fredrik Wilde, Vilhelm Kroon, Cajsa Björkén, Hedda Bring</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126862290</v>
+        <v>126861113</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>97321</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>678323</v>
+        <v>678242</v>
       </c>
       <c r="R77" t="n">
-        <v>7105490</v>
+        <v>7105626</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8569,60 +8561,64 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126862289</v>
+        <v>126861053</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>678303</v>
+        <v>678315</v>
       </c>
       <c r="R78" t="n">
-        <v>7105511</v>
+        <v>7105477</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8666,15 +8662,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8880,10 +8880,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126861046</v>
+        <v>126861212</v>
       </c>
       <c r="B81" t="n">
-        <v>79632</v>
+        <v>91344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8891,21 +8891,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8915,10 +8915,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>678285</v>
+        <v>678349</v>
       </c>
       <c r="R81" t="n">
-        <v>7105527</v>
+        <v>7105698</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8981,48 +8981,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126861080</v>
+        <v>126862284</v>
       </c>
       <c r="B82" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>678337</v>
+        <v>678561</v>
       </c>
       <c r="R82" t="n">
-        <v>7105676</v>
+        <v>7105684</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9066,26 +9066,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126862249</v>
+        <v>126861311</v>
       </c>
       <c r="B83" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9093,37 +9089,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>678565</v>
+        <v>678389</v>
       </c>
       <c r="R83" t="n">
-        <v>7105751</v>
+        <v>7105676</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9167,71 +9163,61 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126861197</v>
+        <v>126861316</v>
       </c>
       <c r="B84" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>678297</v>
+        <v>678325</v>
       </c>
       <c r="R84" t="n">
-        <v>7105488</v>
+        <v>7105669</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9294,45 +9280,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126865255</v>
+        <v>126861046</v>
       </c>
       <c r="B85" t="n">
-        <v>98361</v>
+        <v>79632</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>223591</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>678327</v>
+        <v>678285</v>
       </c>
       <c r="R85" t="n">
-        <v>7105520</v>
+        <v>7105527</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9379,12 +9365,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9395,32 +9381,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126861212</v>
+        <v>126861080</v>
       </c>
       <c r="B86" t="n">
-        <v>91344</v>
+        <v>80146</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9430,10 +9416,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>678349</v>
+        <v>678337</v>
       </c>
       <c r="R86" t="n">
-        <v>7105698</v>
+        <v>7105676</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9485,7 +9471,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9496,10 +9482,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126862284</v>
+        <v>126866144</v>
       </c>
       <c r="B87" t="n">
-        <v>79014</v>
+        <v>96696</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9507,21 +9493,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9531,13 +9517,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>678561</v>
+        <v>678308</v>
       </c>
       <c r="R87" t="n">
-        <v>7105684</v>
+        <v>7105565</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9581,22 +9567,26 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126861311</v>
+        <v>126862249</v>
       </c>
       <c r="B88" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9604,37 +9594,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>678389</v>
+        <v>678565</v>
       </c>
       <c r="R88" t="n">
-        <v>7105676</v>
+        <v>7105751</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9678,61 +9668,71 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126861316</v>
+        <v>126861197</v>
       </c>
       <c r="B89" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>678325</v>
+        <v>678297</v>
       </c>
       <c r="R89" t="n">
-        <v>7105669</v>
+        <v>7105488</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9795,32 +9795,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126866144</v>
+        <v>126865255</v>
       </c>
       <c r="B90" t="n">
-        <v>96696</v>
+        <v>98361</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>53</v>
+        <v>223591</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9830,13 +9830,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>678308</v>
+        <v>678327</v>
       </c>
       <c r="R90" t="n">
-        <v>7105565</v>
+        <v>7105520</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9880,12 +9880,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -11654,10 +11654,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126861054</v>
+        <v>126861188</v>
       </c>
       <c r="B108" t="n">
-        <v>91326</v>
+        <v>78772</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11665,21 +11665,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11689,10 +11689,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>678337</v>
+        <v>678286</v>
       </c>
       <c r="R108" t="n">
-        <v>7105668</v>
+        <v>7105527</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11755,48 +11755,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126866143</v>
+        <v>126868561</v>
       </c>
       <c r="B109" t="n">
-        <v>79046</v>
+        <v>80146</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>678534</v>
+        <v>678322</v>
       </c>
       <c r="R109" t="n">
-        <v>7105769</v>
+        <v>7105572</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11840,12 +11840,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11856,10 +11856,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126861120</v>
+        <v>126865242</v>
       </c>
       <c r="B110" t="n">
-        <v>75133</v>
+        <v>79632</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11867,34 +11867,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>310</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>678361</v>
+        <v>678383</v>
       </c>
       <c r="R110" t="n">
-        <v>7105711</v>
+        <v>7105681</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11941,12 +11941,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -11957,7 +11957,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126861188</v>
+        <v>126861187</v>
       </c>
       <c r="B111" t="n">
         <v>78772</v>
@@ -11992,10 +11992,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>678286</v>
+        <v>678280</v>
       </c>
       <c r="R111" t="n">
-        <v>7105527</v>
+        <v>7105615</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12058,32 +12058,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126868561</v>
+        <v>126861054</v>
       </c>
       <c r="B112" t="n">
-        <v>80146</v>
+        <v>91326</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12093,10 +12093,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>678322</v>
+        <v>678337</v>
       </c>
       <c r="R112" t="n">
-        <v>7105572</v>
+        <v>7105668</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12143,12 +12143,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12159,10 +12159,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126865242</v>
+        <v>126866143</v>
       </c>
       <c r="B113" t="n">
-        <v>79632</v>
+        <v>79046</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12170,21 +12170,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12194,13 +12194,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>678383</v>
+        <v>678534</v>
       </c>
       <c r="R113" t="n">
-        <v>7105681</v>
+        <v>7105769</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12244,12 +12244,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12260,10 +12260,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126861187</v>
+        <v>126861120</v>
       </c>
       <c r="B114" t="n">
-        <v>78772</v>
+        <v>75133</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12271,21 +12271,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>310</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12295,10 +12295,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>678280</v>
+        <v>678361</v>
       </c>
       <c r="R114" t="n">
-        <v>7105615</v>
+        <v>7105711</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13293,48 +13293,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126868618</v>
+        <v>126860446</v>
       </c>
       <c r="B124" t="n">
-        <v>80052</v>
+        <v>78773</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6457</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>678324</v>
+        <v>678302</v>
       </c>
       <c r="R124" t="n">
-        <v>7105582</v>
+        <v>7105594</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13361,9 +13361,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13378,12 +13388,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13394,10 +13404,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126868552</v>
+        <v>126865184</v>
       </c>
       <c r="B125" t="n">
-        <v>79632</v>
+        <v>92809</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13405,34 +13415,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>678377</v>
+        <v>678549</v>
       </c>
       <c r="R125" t="n">
-        <v>7105670</v>
+        <v>7105535</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13476,15 +13486,30 @@
       <c r="AG125" t="b">
         <v>0</v>
       </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13495,10 +13520,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126861167</v>
+        <v>126861263</v>
       </c>
       <c r="B126" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13506,21 +13531,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13530,10 +13555,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>678298</v>
+        <v>678535</v>
       </c>
       <c r="R126" t="n">
-        <v>7105658</v>
+        <v>7105767</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13596,32 +13621,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126861079</v>
+        <v>126868610</v>
       </c>
       <c r="B127" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13631,10 +13656,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>678363</v>
+        <v>678379</v>
       </c>
       <c r="R127" t="n">
-        <v>7105711</v>
+        <v>7105668</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13681,12 +13706,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13697,10 +13722,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126865251</v>
+        <v>126868618</v>
       </c>
       <c r="B128" t="n">
-        <v>80146</v>
+        <v>80052</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13708,34 +13733,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6462</v>
+        <v>6457</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>678319</v>
+        <v>678324</v>
       </c>
       <c r="R128" t="n">
-        <v>7105574</v>
+        <v>7105582</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13779,30 +13804,15 @@
       <c r="AG128" t="b">
         <v>0</v>
       </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13813,32 +13823,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126861336</v>
+        <v>126868552</v>
       </c>
       <c r="B129" t="n">
-        <v>98360</v>
+        <v>79632</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13848,10 +13858,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>678246</v>
+        <v>678377</v>
       </c>
       <c r="R129" t="n">
-        <v>7105631</v>
+        <v>7105670</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13898,12 +13908,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -13914,10 +13924,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126860446</v>
+        <v>126861167</v>
       </c>
       <c r="B130" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13925,37 +13935,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>678302</v>
+        <v>678298</v>
       </c>
       <c r="R130" t="n">
-        <v>7105594</v>
+        <v>7105658</v>
       </c>
       <c r="S130" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13982,19 +13992,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>09:58</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14009,12 +14009,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14025,45 +14025,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126865184</v>
+        <v>126861079</v>
       </c>
       <c r="B131" t="n">
-        <v>92809</v>
+        <v>80146</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>678549</v>
+        <v>678363</v>
       </c>
       <c r="R131" t="n">
-        <v>7105535</v>
+        <v>7105711</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14107,30 +14107,15 @@
       <c r="AG131" t="b">
         <v>0</v>
       </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14141,45 +14126,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126861263</v>
+        <v>126865251</v>
       </c>
       <c r="B132" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>678535</v>
+        <v>678319</v>
       </c>
       <c r="R132" t="n">
-        <v>7105767</v>
+        <v>7105574</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14223,15 +14208,30 @@
       <c r="AG132" t="b">
         <v>0</v>
       </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14242,32 +14242,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126868610</v>
+        <v>126861336</v>
       </c>
       <c r="B133" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>678379</v>
+        <v>678246</v>
       </c>
       <c r="R133" t="n">
-        <v>7105668</v>
+        <v>7105631</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14327,12 +14327,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -19513,10 +19513,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>126865243</v>
+        <v>126866426</v>
       </c>
       <c r="B184" t="n">
-        <v>57817</v>
+        <v>41361</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19524,34 +19524,47 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>103021</v>
+        <v>215713</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>678437</v>
+        <v>678428</v>
       </c>
       <c r="R184" t="n">
-        <v>7105642</v>
+        <v>7105690</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19592,6 +19605,7 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -19603,7 +19617,7 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
@@ -19614,10 +19628,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126866426</v>
+        <v>126866153</v>
       </c>
       <c r="B185" t="n">
-        <v>41361</v>
+        <v>78773</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19625,50 +19639,37 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>215713</v>
+        <v>228912</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>678428</v>
+        <v>678378</v>
       </c>
       <c r="R185" t="n">
-        <v>7105690</v>
+        <v>7105618</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19706,19 +19707,18 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
@@ -19729,10 +19729,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>126866153</v>
+        <v>126865243</v>
       </c>
       <c r="B186" t="n">
-        <v>78773</v>
+        <v>57817</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19740,21 +19740,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19764,13 +19764,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>678378</v>
+        <v>678437</v>
       </c>
       <c r="R186" t="n">
-        <v>7105618</v>
+        <v>7105642</v>
       </c>
       <c r="S186" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19814,12 +19814,12 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
@@ -19830,10 +19830,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>126861048</v>
+        <v>126861173</v>
       </c>
       <c r="B187" t="n">
-        <v>79046</v>
+        <v>80117</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19841,21 +19841,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19865,10 +19865,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>678521</v>
+        <v>678296</v>
       </c>
       <c r="R187" t="n">
-        <v>7105765</v>
+        <v>7105491</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19931,45 +19931,45 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>126865183</v>
+        <v>126861103</v>
       </c>
       <c r="B188" t="n">
-        <v>78681</v>
+        <v>80021</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>353</v>
+        <v>6456</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>678508</v>
+        <v>678269</v>
       </c>
       <c r="R188" t="n">
-        <v>7105521</v>
+        <v>7105598</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20013,30 +20013,15 @@
       <c r="AG188" t="b">
         <v>0</v>
       </c>
-      <c r="AJ188" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO188" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
@@ -20047,10 +20032,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>126865182</v>
+        <v>126862243</v>
       </c>
       <c r="B189" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20058,37 +20043,37 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>678390</v>
+        <v>678523</v>
       </c>
       <c r="R189" t="n">
-        <v>7105570</v>
+        <v>7105789</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20128,45 +20113,26 @@
       </c>
       <c r="AG189" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO189" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY189" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>126861261</v>
+        <v>126868589</v>
       </c>
       <c r="B190" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20174,21 +20140,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20198,10 +20164,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>678484</v>
+        <v>678328</v>
       </c>
       <c r="R190" t="n">
-        <v>7105705</v>
+        <v>7105581</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20248,12 +20214,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -20264,7 +20230,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>126861326</v>
+        <v>126865182</v>
       </c>
       <c r="B191" t="n">
         <v>79014</v>
@@ -20295,14 +20261,14 @@
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>678283</v>
+        <v>678390</v>
       </c>
       <c r="R191" t="n">
-        <v>7105602</v>
+        <v>7105570</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20346,15 +20312,30 @@
       <c r="AG191" t="b">
         <v>0</v>
       </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -20365,7 +20346,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>126865763</v>
+        <v>126861261</v>
       </c>
       <c r="B192" t="n">
         <v>79014</v>
@@ -20394,19 +20375,16 @@
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>678314</v>
+        <v>678484</v>
       </c>
       <c r="R192" t="n">
-        <v>7105612</v>
+        <v>7105705</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20447,19 +20425,18 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -20470,10 +20447,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126861173</v>
+        <v>126861326</v>
       </c>
       <c r="B193" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20481,21 +20458,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20505,10 +20482,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>678296</v>
+        <v>678283</v>
       </c>
       <c r="R193" t="n">
-        <v>7105491</v>
+        <v>7105602</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20571,45 +20548,48 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126861103</v>
+        <v>126865763</v>
       </c>
       <c r="B194" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>678269</v>
+        <v>678314</v>
       </c>
       <c r="R194" t="n">
-        <v>7105598</v>
+        <v>7105612</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20650,18 +20630,19 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -20672,10 +20653,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126862243</v>
+        <v>126861048</v>
       </c>
       <c r="B195" t="n">
-        <v>79632</v>
+        <v>79046</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20683,37 +20664,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>678523</v>
+        <v>678521</v>
       </c>
       <c r="R195" t="n">
-        <v>7105789</v>
+        <v>7105765</v>
       </c>
       <c r="S195" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -20757,22 +20738,26 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY195" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126868589</v>
+        <v>126865183</v>
       </c>
       <c r="B196" t="n">
-        <v>80117</v>
+        <v>78681</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20780,34 +20765,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>678328</v>
+        <v>678508</v>
       </c>
       <c r="R196" t="n">
-        <v>7105581</v>
+        <v>7105521</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20851,15 +20836,30 @@
       <c r="AG196" t="b">
         <v>0</v>
       </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
@@ -23047,10 +23047,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>126866090</v>
+        <v>126865996</v>
       </c>
       <c r="B218" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23058,43 +23058,26 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
@@ -23102,10 +23085,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>678594</v>
+        <v>678605</v>
       </c>
       <c r="R218" t="n">
-        <v>7105682</v>
+        <v>7105707</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23146,6 +23129,7 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
+      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
@@ -23157,7 +23141,7 @@
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Fredrik Wilde, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
@@ -23168,10 +23152,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>126865996</v>
+        <v>126866090</v>
       </c>
       <c r="B219" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23179,26 +23163,43 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
@@ -23206,10 +23207,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>678605</v>
+        <v>678594</v>
       </c>
       <c r="R219" t="n">
-        <v>7105707</v>
+        <v>7105682</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23250,7 +23251,6 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
-      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -23262,7 +23262,7 @@
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Fredrik Wilde, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
@@ -23888,10 +23888,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>126865442</v>
+        <v>126865445</v>
       </c>
       <c r="B226" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23899,21 +23899,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23923,10 +23923,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>678295</v>
+        <v>678319</v>
       </c>
       <c r="R226" t="n">
-        <v>7105600</v>
+        <v>7105572</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23989,10 +23989,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>126865445</v>
+        <v>126865442</v>
       </c>
       <c r="B227" t="n">
-        <v>80117</v>
+        <v>78773</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24000,21 +24000,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24024,10 +24024,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>678319</v>
+        <v>678295</v>
       </c>
       <c r="R227" t="n">
-        <v>7105572</v>
+        <v>7105600</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -1311,45 +1311,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126811407</v>
+        <v>126814992</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>678303</v>
+        <v>678336</v>
       </c>
       <c r="R8" t="n">
-        <v>7105499</v>
+        <v>7105495</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,66 +1405,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126814992</v>
+        <v>126811407</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Råtjärnen, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>678336</v>
+        <v>678303</v>
       </c>
       <c r="R9" t="n">
-        <v>7105495</v>
+        <v>7105499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,12 +1502,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126861142</v>
+        <v>126860448</v>
       </c>
       <c r="B19" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,37 +2417,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>678244</v>
+        <v>678446</v>
       </c>
       <c r="R19" t="n">
-        <v>7105642</v>
+        <v>7105699</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2474,14 +2474,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2496,12 +2501,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2512,10 +2517,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126865187</v>
+        <v>126861142</v>
       </c>
       <c r="B20" t="n">
-        <v>78420</v>
+        <v>80117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2523,34 +2528,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>678622</v>
+        <v>678244</v>
       </c>
       <c r="R20" t="n">
-        <v>7105605</v>
+        <v>7105642</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2585,6 +2590,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2593,31 +2603,16 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2628,7 +2623,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126861312</v>
+        <v>126861260</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2663,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>678383</v>
+        <v>678449</v>
       </c>
       <c r="R21" t="n">
-        <v>7105668</v>
+        <v>7105699</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2729,45 +2724,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126861083</v>
+        <v>126865187</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>78420</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>678271</v>
+        <v>678622</v>
       </c>
       <c r="R22" t="n">
-        <v>7105610</v>
+        <v>7105605</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,15 +2806,30 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2830,32 +2840,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126861081</v>
+        <v>126861312</v>
       </c>
       <c r="B23" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2865,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>678254</v>
+        <v>678383</v>
       </c>
       <c r="R23" t="n">
-        <v>7105631</v>
+        <v>7105668</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2931,32 +2941,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126861260</v>
+        <v>126861083</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2966,10 +2976,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>678449</v>
+        <v>678271</v>
       </c>
       <c r="R24" t="n">
-        <v>7105699</v>
+        <v>7105610</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,48 +3042,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126860448</v>
+        <v>126861081</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>678446</v>
+        <v>678254</v>
       </c>
       <c r="R25" t="n">
-        <v>7105699</v>
+        <v>7105631</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3100,19 +3110,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3127,12 +3127,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -5103,10 +5103,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126861056</v>
+        <v>126865246</v>
       </c>
       <c r="B45" t="n">
-        <v>91326</v>
+        <v>57817</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5114,34 +5114,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>678315</v>
+        <v>678584</v>
       </c>
       <c r="R45" t="n">
-        <v>7105477</v>
+        <v>7105735</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,12 +5188,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5204,45 +5204,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126865181</v>
+        <v>126861122</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>678324</v>
+        <v>678233</v>
       </c>
       <c r="R46" t="n">
-        <v>7105598</v>
+        <v>7105643</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5286,30 +5291,15 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5320,32 +5310,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126862286</v>
+        <v>126866161</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5355,13 +5345,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>678452</v>
+        <v>678315</v>
       </c>
       <c r="R47" t="n">
-        <v>7105602</v>
+        <v>7105536</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5405,44 +5395,48 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126861104</v>
+        <v>126861056</v>
       </c>
       <c r="B48" t="n">
-        <v>80021</v>
+        <v>91326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5452,10 +5446,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>678269</v>
+        <v>678315</v>
       </c>
       <c r="R48" t="n">
-        <v>7105603</v>
+        <v>7105477</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5518,10 +5512,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126865757</v>
+        <v>126865181</v>
       </c>
       <c r="B49" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5529,37 +5523,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>678290</v>
+        <v>678324</v>
       </c>
       <c r="R49" t="n">
-        <v>7105528</v>
+        <v>7105598</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5600,19 +5591,33 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5623,10 +5628,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126865186</v>
+        <v>126862286</v>
       </c>
       <c r="B50" t="n">
-        <v>77992</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5634,37 +5639,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>678622</v>
+        <v>678452</v>
       </c>
       <c r="R50" t="n">
-        <v>7105605</v>
+        <v>7105602</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5704,83 +5709,64 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126850977</v>
+        <v>126861104</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>80021</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>678347</v>
+        <v>678269</v>
       </c>
       <c r="R51" t="n">
-        <v>7105602</v>
+        <v>7105603</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5807,19 +5793,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5834,12 +5810,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5850,50 +5826,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126861122</v>
+        <v>126865757</v>
       </c>
       <c r="B52" t="n">
-        <v>8447</v>
+        <v>78772</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>678233</v>
+        <v>678290</v>
       </c>
       <c r="R52" t="n">
-        <v>7105643</v>
+        <v>7105528</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5934,18 +5908,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5956,48 +5931,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126866161</v>
+        <v>126850977</v>
       </c>
       <c r="B53" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>678315</v>
+        <v>678347</v>
       </c>
       <c r="R53" t="n">
-        <v>7105536</v>
+        <v>7105602</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6024,9 +5999,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6041,12 +6026,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6057,10 +6042,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126865246</v>
+        <v>126865186</v>
       </c>
       <c r="B54" t="n">
-        <v>57817</v>
+        <v>77992</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6068,34 +6053,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>678584</v>
+        <v>678622</v>
       </c>
       <c r="R54" t="n">
-        <v>7105735</v>
+        <v>7105605</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6139,15 +6124,30 @@
       <c r="AG54" t="b">
         <v>0</v>
       </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6356,48 +6356,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126868577</v>
+        <v>126850880</v>
       </c>
       <c r="B57" t="n">
-        <v>75133</v>
+        <v>98443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>310</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>678313</v>
+        <v>678346</v>
       </c>
       <c r="R57" t="n">
-        <v>7105562</v>
+        <v>7105594</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6424,9 +6433,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6441,12 +6460,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6457,48 +6476,52 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126866163</v>
+        <v>126860443</v>
       </c>
       <c r="B58" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>678468</v>
+        <v>678344</v>
       </c>
       <c r="R58" t="n">
-        <v>7105617</v>
+        <v>7105500</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6525,9 +6548,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6542,12 +6575,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6558,51 +6591,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126865759</v>
+        <v>126866163</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>678614</v>
+        <v>678468</v>
       </c>
       <c r="R59" t="n">
-        <v>7105648</v>
+        <v>7105617</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6640,19 +6670,18 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6663,10 +6692,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126851831</v>
+        <v>126868577</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>75133</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6674,37 +6703,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>678360</v>
+        <v>678313</v>
       </c>
       <c r="R60" t="n">
-        <v>7105719</v>
+        <v>7105562</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6731,19 +6760,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>10:46</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>10:46</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6758,12 +6777,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6774,10 +6793,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126861170</v>
+        <v>126865759</v>
       </c>
       <c r="B61" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6785,34 +6804,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>678251</v>
+        <v>678614</v>
       </c>
       <c r="R61" t="n">
-        <v>7105649</v>
+        <v>7105648</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6853,18 +6875,19 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6875,10 +6898,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126863389</v>
+        <v>126851831</v>
       </c>
       <c r="B62" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6886,37 +6909,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>678532</v>
+        <v>678360</v>
       </c>
       <c r="R62" t="n">
-        <v>7105778</v>
+        <v>7105719</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6943,9 +6966,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6960,12 +6993,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6976,57 +7009,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126850880</v>
+        <v>126861170</v>
       </c>
       <c r="B63" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>678346</v>
+        <v>678251</v>
       </c>
       <c r="R63" t="n">
-        <v>7105594</v>
+        <v>7105649</v>
       </c>
       <c r="S63" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7053,19 +7077,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7080,12 +7094,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7096,52 +7110,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126860443</v>
+        <v>126863389</v>
       </c>
       <c r="B64" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>678344</v>
+        <v>678532</v>
       </c>
       <c r="R64" t="n">
-        <v>7105500</v>
+        <v>7105778</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7168,19 +7178,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:42</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7195,12 +7195,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -9896,10 +9896,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126861082</v>
+        <v>126867967</v>
       </c>
       <c r="B91" t="n">
-        <v>80146</v>
+        <v>98360</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9907,34 +9907,38 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>678240</v>
+        <v>678532</v>
       </c>
       <c r="R91" t="n">
-        <v>7105623</v>
+        <v>7105782</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9975,18 +9979,19 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Lotta Ihse, Mattias Dalkvist, Anne Siivola, Malin Löfgren, Philipp Weiss, Carl Jansson, Peder Winding, Martin Axegård, Fredrik Wilde, Vilhelm Kroon, Cajsa Björkén, Hedda Bring</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9997,45 +10002,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126868553</v>
+        <v>126863396</v>
       </c>
       <c r="B92" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>678439</v>
+        <v>678396</v>
       </c>
       <c r="R92" t="n">
-        <v>7105679</v>
+        <v>7105690</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10082,12 +10087,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10098,10 +10103,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126861265</v>
+        <v>126861172</v>
       </c>
       <c r="B93" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10109,21 +10114,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10133,10 +10138,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>678512</v>
+        <v>678290</v>
       </c>
       <c r="R93" t="n">
-        <v>7105771</v>
+        <v>7105503</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10199,10 +10204,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126862292</v>
+        <v>126865284</v>
       </c>
       <c r="B94" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10210,37 +10215,40 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>678338</v>
+        <v>678332</v>
       </c>
       <c r="R94" t="n">
-        <v>7105482</v>
+        <v>7105581</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10280,26 +10288,45 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126861172</v>
+        <v>126853137</v>
       </c>
       <c r="B95" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10307,37 +10334,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>678290</v>
+        <v>678510</v>
       </c>
       <c r="R95" t="n">
-        <v>7105503</v>
+        <v>7105573</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10364,9 +10391,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10381,12 +10418,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10397,10 +10434,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126865284</v>
+        <v>126868553</v>
       </c>
       <c r="B96" t="n">
-        <v>80117</v>
+        <v>91326</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10408,37 +10445,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>678332</v>
+        <v>678439</v>
       </c>
       <c r="R96" t="n">
-        <v>7105581</v>
+        <v>7105679</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10482,30 +10516,15 @@
       <c r="AG96" t="b">
         <v>0</v>
       </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10516,7 +10535,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126853137</v>
+        <v>126861265</v>
       </c>
       <c r="B97" t="n">
         <v>79014</v>
@@ -10547,17 +10566,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>678510</v>
+        <v>678512</v>
       </c>
       <c r="R97" t="n">
-        <v>7105573</v>
+        <v>7105771</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10584,19 +10603,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10611,12 +10620,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10627,52 +10636,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126867967</v>
+        <v>126862292</v>
       </c>
       <c r="B98" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>678532</v>
+        <v>678338</v>
       </c>
       <c r="R98" t="n">
-        <v>7105782</v>
+        <v>7105482</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10710,68 +10715,63 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Mattias Dalkvist, Anne Siivola, Malin Löfgren, Philipp Weiss, Carl Jansson, Peder Winding, Martin Axegård, Fredrik Wilde, Vilhelm Kroon, Cajsa Björkén, Hedda Bring</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126863396</v>
+        <v>126861082</v>
       </c>
       <c r="B99" t="n">
-        <v>98443</v>
+        <v>80146</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>678396</v>
+        <v>678240</v>
       </c>
       <c r="R99" t="n">
-        <v>7105690</v>
+        <v>7105623</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10818,12 +10818,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10834,10 +10834,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126866143</v>
+        <v>126861313</v>
       </c>
       <c r="B100" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10845,37 +10845,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>678534</v>
+        <v>678377</v>
       </c>
       <c r="R100" t="n">
-        <v>7105769</v>
+        <v>7105664</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10919,12 +10919,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10935,7 +10935,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126861313</v>
+        <v>126866158</v>
       </c>
       <c r="B101" t="n">
         <v>79014</v>
@@ -10966,17 +10966,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>678377</v>
+        <v>678283</v>
       </c>
       <c r="R101" t="n">
-        <v>7105664</v>
+        <v>7105510</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11020,12 +11020,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11036,7 +11036,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126866158</v>
+        <v>126861321</v>
       </c>
       <c r="B102" t="n">
         <v>79014</v>
@@ -11067,17 +11067,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
         <v>678283</v>
       </c>
       <c r="R102" t="n">
-        <v>7105510</v>
+        <v>7105646</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11121,12 +11121,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11137,7 +11137,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126861321</v>
+        <v>126861325</v>
       </c>
       <c r="B103" t="n">
         <v>79014</v>
@@ -11172,10 +11172,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>678283</v>
+        <v>678282</v>
       </c>
       <c r="R103" t="n">
-        <v>7105646</v>
+        <v>7105617</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11238,7 +11238,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126861325</v>
+        <v>126864769</v>
       </c>
       <c r="B104" t="n">
         <v>79014</v>
@@ -11267,16 +11267,19 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>678282</v>
+        <v>678334</v>
       </c>
       <c r="R104" t="n">
-        <v>7105617</v>
+        <v>7105667</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11317,18 +11320,19 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Lotta Ihse, Malin Löfgren, Mattias Dalkvist, Anne Siivola, Philipp Weiss, Carl Jansson, Peder Winding, Martin Axegård, Fredrik Wilde, Vilhelm Kroon, Cajsa Björkén, Hedda Bring</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11339,7 +11343,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126864769</v>
+        <v>126861258</v>
       </c>
       <c r="B105" t="n">
         <v>79014</v>
@@ -11368,19 +11372,16 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>678334</v>
+        <v>678408</v>
       </c>
       <c r="R105" t="n">
-        <v>7105667</v>
+        <v>7105700</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11421,19 +11422,18 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Malin Löfgren, Mattias Dalkvist, Anne Siivola, Philipp Weiss, Carl Jansson, Peder Winding, Martin Axegård, Fredrik Wilde, Vilhelm Kroon, Cajsa Björkén, Hedda Bring</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11444,10 +11444,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126861258</v>
+        <v>126861188</v>
       </c>
       <c r="B106" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11455,21 +11455,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11479,10 +11479,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>678408</v>
+        <v>678286</v>
       </c>
       <c r="R106" t="n">
-        <v>7105700</v>
+        <v>7105527</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11545,10 +11545,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126861188</v>
+        <v>126865242</v>
       </c>
       <c r="B107" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11556,34 +11556,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>678286</v>
+        <v>678383</v>
       </c>
       <c r="R107" t="n">
-        <v>7105527</v>
+        <v>7105681</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11630,12 +11630,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11646,10 +11646,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126865242</v>
+        <v>126861187</v>
       </c>
       <c r="B108" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11657,34 +11657,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>678383</v>
+        <v>678280</v>
       </c>
       <c r="R108" t="n">
-        <v>7105681</v>
+        <v>7105615</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11731,12 +11731,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11747,32 +11747,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126861187</v>
+        <v>126868561</v>
       </c>
       <c r="B109" t="n">
-        <v>78772</v>
+        <v>80146</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11782,10 +11782,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>678280</v>
+        <v>678322</v>
       </c>
       <c r="R109" t="n">
-        <v>7105615</v>
+        <v>7105572</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11832,12 +11832,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11848,10 +11848,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126862245</v>
+        <v>126861120</v>
       </c>
       <c r="B110" t="n">
-        <v>57657</v>
+        <v>75133</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11859,37 +11859,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>678530</v>
+        <v>678361</v>
       </c>
       <c r="R110" t="n">
-        <v>7105781</v>
+        <v>7105711</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11933,22 +11933,26 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126868554</v>
+        <v>126866143</v>
       </c>
       <c r="B111" t="n">
-        <v>57657</v>
+        <v>79046</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11956,49 +11960,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
         <v>678534</v>
       </c>
       <c r="R111" t="n">
-        <v>7105773</v>
+        <v>7105769</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12042,12 +12034,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12058,10 +12050,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126861120</v>
+        <v>126861054</v>
       </c>
       <c r="B112" t="n">
-        <v>75133</v>
+        <v>91326</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12069,21 +12061,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>310</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12093,10 +12085,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>678361</v>
+        <v>678337</v>
       </c>
       <c r="R112" t="n">
-        <v>7105711</v>
+        <v>7105668</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12159,10 +12151,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126861054</v>
+        <v>126862245</v>
       </c>
       <c r="B113" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12170,37 +12162,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>678337</v>
+        <v>678530</v>
       </c>
       <c r="R113" t="n">
-        <v>7105668</v>
+        <v>7105781</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12244,61 +12236,69 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126868561</v>
+        <v>126868554</v>
       </c>
       <c r="B114" t="n">
-        <v>80146</v>
+        <v>57657</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>678322</v>
+        <v>678534</v>
       </c>
       <c r="R114" t="n">
-        <v>7105572</v>
+        <v>7105773</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12361,10 +12361,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126865185</v>
+        <v>126868550</v>
       </c>
       <c r="B115" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12372,34 +12372,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>678603</v>
+        <v>678293</v>
       </c>
       <c r="R115" t="n">
-        <v>7105573</v>
+        <v>7105493</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12443,30 +12443,15 @@
       <c r="AG115" t="b">
         <v>0</v>
       </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12477,51 +12462,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126865226</v>
+        <v>126862267</v>
       </c>
       <c r="B116" t="n">
-        <v>80146</v>
+        <v>80117</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>678313</v>
+        <v>678314</v>
       </c>
       <c r="R116" t="n">
-        <v>7105600</v>
+        <v>7105563</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12559,67 +12541,66 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126862274</v>
+        <v>126865185</v>
       </c>
       <c r="B117" t="n">
-        <v>58334</v>
+        <v>79014</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>678512</v>
+        <v>678603</v>
       </c>
       <c r="R117" t="n">
-        <v>7105616</v>
+        <v>7105573</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12659,64 +12640,86 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr"/>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126852438</v>
+        <v>126865226</v>
       </c>
       <c r="B118" t="n">
-        <v>78773</v>
+        <v>80146</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>678438</v>
+        <v>678313</v>
       </c>
       <c r="R118" t="n">
-        <v>7105684</v>
+        <v>7105600</v>
       </c>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12743,53 +12746,40 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126865316</v>
+        <v>126853157</v>
       </c>
       <c r="B119" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12797,34 +12787,38 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>678353</v>
+        <v>678507</v>
       </c>
       <c r="R119" t="n">
-        <v>7105503</v>
+        <v>7105595</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12854,9 +12848,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12871,64 +12875,60 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126868550</v>
+        <v>126862297</v>
       </c>
       <c r="B120" t="n">
-        <v>79632</v>
+        <v>98360</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>678293</v>
+        <v>678417</v>
       </c>
       <c r="R120" t="n">
-        <v>7105493</v>
+        <v>7105592</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12972,26 +12972,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126862267</v>
+        <v>126852438</v>
       </c>
       <c r="B121" t="n">
-        <v>80117</v>
+        <v>78773</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12999,37 +12995,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>678314</v>
+        <v>678438</v>
       </c>
       <c r="R121" t="n">
-        <v>7105563</v>
+        <v>7105684</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13056,9 +13052,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13073,64 +13079,64 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr"/>
+          <t>Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126853157</v>
+        <v>126862274</v>
       </c>
       <c r="B122" t="n">
-        <v>57817</v>
+        <v>58334</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>678507</v>
+        <v>678512</v>
       </c>
       <c r="R122" t="n">
-        <v>7105595</v>
+        <v>7105616</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13157,19 +13163,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13184,44 +13180,44 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126862297</v>
+        <v>126865316</v>
       </c>
       <c r="B123" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13231,13 +13227,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>678417</v>
+        <v>678353</v>
       </c>
       <c r="R123" t="n">
-        <v>7105592</v>
+        <v>7105503</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13281,15 +13277,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr"/>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14343,7 +14343,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126861137</v>
+        <v>126861138</v>
       </c>
       <c r="B134" t="n">
         <v>78773</v>
@@ -14378,10 +14378,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>678270</v>
+        <v>678295</v>
       </c>
       <c r="R134" t="n">
-        <v>7105627</v>
+        <v>7105595</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14444,10 +14444,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126861138</v>
+        <v>126861322</v>
       </c>
       <c r="B135" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14455,21 +14455,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14479,10 +14479,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>678295</v>
+        <v>678224</v>
       </c>
       <c r="R135" t="n">
-        <v>7105595</v>
+        <v>7105630</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14545,10 +14545,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126868588</v>
+        <v>126861262</v>
       </c>
       <c r="B136" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14556,21 +14556,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14580,10 +14580,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>678330</v>
+        <v>678532</v>
       </c>
       <c r="R136" t="n">
-        <v>7105451</v>
+        <v>7105725</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14630,12 +14630,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14646,7 +14646,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126862287</v>
+        <v>126861315</v>
       </c>
       <c r="B137" t="n">
         <v>79014</v>
@@ -14677,17 +14677,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>678359</v>
+        <v>678354</v>
       </c>
       <c r="R137" t="n">
-        <v>7105587</v>
+        <v>7105657</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14731,22 +14731,26 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY137" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126861322</v>
+        <v>126868588</v>
       </c>
       <c r="B138" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14754,21 +14758,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14778,10 +14782,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>678224</v>
+        <v>678330</v>
       </c>
       <c r="R138" t="n">
-        <v>7105630</v>
+        <v>7105451</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14828,12 +14832,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14844,48 +14848,48 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126861105</v>
+        <v>126862287</v>
       </c>
       <c r="B139" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>678330</v>
+        <v>678359</v>
       </c>
       <c r="R139" t="n">
-        <v>7105447</v>
+        <v>7105587</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14929,26 +14933,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126868617</v>
+        <v>126861105</v>
       </c>
       <c r="B140" t="n">
-        <v>80052</v>
+        <v>80021</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14956,21 +14956,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14980,10 +14980,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>678328</v>
+        <v>678330</v>
       </c>
       <c r="R140" t="n">
-        <v>7105581</v>
+        <v>7105447</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15030,12 +15030,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15046,32 +15046,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126861307</v>
+        <v>126868617</v>
       </c>
       <c r="B141" t="n">
-        <v>79014</v>
+        <v>80052</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15081,10 +15081,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>678356</v>
+        <v>678328</v>
       </c>
       <c r="R141" t="n">
-        <v>7105708</v>
+        <v>7105581</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15131,12 +15131,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15147,7 +15147,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126861309</v>
+        <v>126861307</v>
       </c>
       <c r="B142" t="n">
         <v>79014</v>
@@ -15182,10 +15182,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>678368</v>
+        <v>678356</v>
       </c>
       <c r="R142" t="n">
-        <v>7105697</v>
+        <v>7105708</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15248,7 +15248,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126861262</v>
+        <v>126861309</v>
       </c>
       <c r="B143" t="n">
         <v>79014</v>
@@ -15283,10 +15283,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>678532</v>
+        <v>678368</v>
       </c>
       <c r="R143" t="n">
-        <v>7105725</v>
+        <v>7105697</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15349,10 +15349,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126861315</v>
+        <v>126861137</v>
       </c>
       <c r="B144" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15360,21 +15360,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15384,10 +15384,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>678354</v>
+        <v>678270</v>
       </c>
       <c r="R144" t="n">
-        <v>7105657</v>
+        <v>7105627</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17340,57 +17340,48 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126861196</v>
+        <v>126862271</v>
       </c>
       <c r="B163" t="n">
-        <v>98443</v>
+        <v>92091</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>678405</v>
+        <v>678309</v>
       </c>
       <c r="R163" t="n">
-        <v>7105696</v>
+        <v>7105559</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17434,26 +17425,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126862271</v>
+        <v>126866162</v>
       </c>
       <c r="B164" t="n">
-        <v>92091</v>
+        <v>78681</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17461,21 +17448,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17485,13 +17472,13 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>678309</v>
+        <v>678495</v>
       </c>
       <c r="R164" t="n">
-        <v>7105559</v>
+        <v>7105613</v>
       </c>
       <c r="S164" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17535,22 +17522,26 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126866162</v>
+        <v>126861320</v>
       </c>
       <c r="B165" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17558,37 +17549,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>678495</v>
+        <v>678306</v>
       </c>
       <c r="R165" t="n">
-        <v>7105613</v>
+        <v>7105658</v>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17632,12 +17623,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17648,7 +17639,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126861320</v>
+        <v>126861308</v>
       </c>
       <c r="B166" t="n">
         <v>79014</v>
@@ -17683,10 +17674,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>678306</v>
+        <v>678365</v>
       </c>
       <c r="R166" t="n">
-        <v>7105658</v>
+        <v>7105710</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17749,7 +17740,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126861308</v>
+        <v>126862283</v>
       </c>
       <c r="B167" t="n">
         <v>79014</v>
@@ -17780,17 +17771,17 @@
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>678365</v>
+        <v>678643</v>
       </c>
       <c r="R167" t="n">
-        <v>7105710</v>
+        <v>7105684</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17834,23 +17825,19 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY167" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126862283</v>
+        <v>126861323</v>
       </c>
       <c r="B168" t="n">
         <v>79014</v>
@@ -17881,17 +17868,17 @@
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>678643</v>
+        <v>678250</v>
       </c>
       <c r="R168" t="n">
-        <v>7105684</v>
+        <v>7105611</v>
       </c>
       <c r="S168" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17935,19 +17922,23 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY168" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126861323</v>
+        <v>126862282</v>
       </c>
       <c r="B169" t="n">
         <v>79014</v>
@@ -17978,17 +17969,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>678250</v>
+        <v>678519</v>
       </c>
       <c r="R169" t="n">
-        <v>7105611</v>
+        <v>7105769</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18032,26 +18023,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY169" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126861107</v>
+        <v>126861264</v>
       </c>
       <c r="B170" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18059,39 +18046,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>678356</v>
+        <v>678524</v>
       </c>
       <c r="R170" t="n">
-        <v>7105710</v>
+        <v>7105764</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18124,11 +18106,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Äldr ringhack (gran)</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18159,10 +18136,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126862282</v>
+        <v>126861107</v>
       </c>
       <c r="B171" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18170,37 +18147,42 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>678519</v>
+        <v>678356</v>
       </c>
       <c r="R171" t="n">
-        <v>7105769</v>
+        <v>7105710</v>
       </c>
       <c r="S171" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18230,6 +18212,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Äldr ringhack (gran)</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18244,60 +18231,68 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY171" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126861264</v>
+        <v>126851795</v>
       </c>
       <c r="B172" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>678524</v>
+        <v>678356</v>
       </c>
       <c r="R172" t="n">
-        <v>7105764</v>
+        <v>7105581</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18324,9 +18319,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18341,12 +18346,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -18357,7 +18362,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126851795</v>
+        <v>126861196</v>
       </c>
       <c r="B173" t="n">
         <v>98443</v>
@@ -18387,22 +18392,27 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>678356</v>
+        <v>678405</v>
       </c>
       <c r="R173" t="n">
-        <v>7105581</v>
+        <v>7105696</v>
       </c>
       <c r="S173" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18429,19 +18439,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18456,12 +18456,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -19296,10 +19296,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>126866142</v>
+        <v>126866426</v>
       </c>
       <c r="B182" t="n">
-        <v>75138</v>
+        <v>41361</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19307,37 +19307,50 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6440</v>
+        <v>215713</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>678327</v>
+        <v>678428</v>
       </c>
       <c r="R182" t="n">
-        <v>7105562</v>
+        <v>7105690</v>
       </c>
       <c r="S182" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19375,18 +19388,19 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
+      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -19397,7 +19411,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>126865238</v>
+        <v>126866142</v>
       </c>
       <c r="B183" t="n">
         <v>75138</v>
@@ -19432,13 +19446,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>678313</v>
+        <v>678327</v>
       </c>
       <c r="R183" t="n">
-        <v>7105554</v>
+        <v>7105562</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -19482,12 +19496,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -19498,45 +19512,45 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>126865180</v>
+        <v>126865238</v>
       </c>
       <c r="B184" t="n">
-        <v>80052</v>
+        <v>75138</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6457</v>
+        <v>6440</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q184" t="n">
         <v>678313</v>
       </c>
       <c r="R184" t="n">
-        <v>7105563</v>
+        <v>7105554</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19580,30 +19594,15 @@
       <c r="AG184" t="b">
         <v>0</v>
       </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
@@ -19614,58 +19613,45 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126866426</v>
+        <v>126865180</v>
       </c>
       <c r="B185" t="n">
-        <v>41361</v>
+        <v>80052</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>215713</v>
+        <v>6457</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>678428</v>
+        <v>678313</v>
       </c>
       <c r="R185" t="n">
-        <v>7105690</v>
+        <v>7105563</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19706,19 +19692,33 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
@@ -19946,32 +19946,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>126861103</v>
+        <v>126861048</v>
       </c>
       <c r="B188" t="n">
-        <v>80021</v>
+        <v>79046</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19981,10 +19981,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>678269</v>
+        <v>678521</v>
       </c>
       <c r="R188" t="n">
-        <v>7105598</v>
+        <v>7105765</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20047,10 +20047,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>126862243</v>
+        <v>126865182</v>
       </c>
       <c r="B189" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20058,37 +20058,37 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>678523</v>
+        <v>678390</v>
       </c>
       <c r="R189" t="n">
-        <v>7105789</v>
+        <v>7105570</v>
       </c>
       <c r="S189" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20128,26 +20128,45 @@
       </c>
       <c r="AG189" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY189" t="inlineStr"/>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>126861173</v>
+        <v>126861261</v>
       </c>
       <c r="B190" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20155,21 +20174,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20179,10 +20198,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>678296</v>
+        <v>678484</v>
       </c>
       <c r="R190" t="n">
-        <v>7105491</v>
+        <v>7105705</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20245,32 +20264,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>126868589</v>
+        <v>126861103</v>
       </c>
       <c r="B191" t="n">
-        <v>80117</v>
+        <v>80021</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20280,10 +20299,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>678328</v>
+        <v>678269</v>
       </c>
       <c r="R191" t="n">
-        <v>7105581</v>
+        <v>7105598</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20330,12 +20349,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -20346,10 +20365,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>126861048</v>
+        <v>126862243</v>
       </c>
       <c r="B192" t="n">
-        <v>79046</v>
+        <v>79632</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20357,37 +20376,37 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>678521</v>
+        <v>678523</v>
       </c>
       <c r="R192" t="n">
-        <v>7105765</v>
+        <v>7105789</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -20431,26 +20450,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY192" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126865182</v>
+        <v>126861173</v>
       </c>
       <c r="B193" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20458,34 +20473,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>678390</v>
+        <v>678296</v>
       </c>
       <c r="R193" t="n">
-        <v>7105570</v>
+        <v>7105491</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20529,30 +20544,15 @@
       <c r="AG193" t="b">
         <v>0</v>
       </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO193" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -20563,10 +20563,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126861261</v>
+        <v>126868589</v>
       </c>
       <c r="B194" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20574,21 +20574,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20598,10 +20598,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>678484</v>
+        <v>678328</v>
       </c>
       <c r="R194" t="n">
-        <v>7105705</v>
+        <v>7105581</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20648,12 +20648,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -21186,49 +21186,45 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126868614</v>
+        <v>126868551</v>
       </c>
       <c r="B200" t="n">
-        <v>98360</v>
+        <v>79632</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>678329</v>
+        <v>678369</v>
       </c>
       <c r="R200" t="n">
-        <v>7105527</v>
+        <v>7105652</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21291,32 +21287,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>126861139</v>
+        <v>126868616</v>
       </c>
       <c r="B201" t="n">
-        <v>78773</v>
+        <v>80052</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>228912</v>
+        <v>6457</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21326,10 +21322,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>678244</v>
+        <v>678314</v>
       </c>
       <c r="R201" t="n">
-        <v>7105643</v>
+        <v>7105567</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21376,12 +21372,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -21392,10 +21388,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>126866155</v>
+        <v>126868597</v>
       </c>
       <c r="B202" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21403,37 +21399,37 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>678318</v>
+        <v>678369</v>
       </c>
       <c r="R202" t="n">
-        <v>7105498</v>
+        <v>7105652</v>
       </c>
       <c r="S202" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21477,12 +21473,12 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -21493,45 +21489,49 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>126863395</v>
+        <v>126868614</v>
       </c>
       <c r="B203" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>678285</v>
+        <v>678329</v>
       </c>
       <c r="R203" t="n">
-        <v>7105493</v>
+        <v>7105527</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21578,12 +21578,12 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
@@ -21594,54 +21594,45 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>126861201</v>
+        <v>126861139</v>
       </c>
       <c r="B204" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>678275</v>
+        <v>678244</v>
       </c>
       <c r="R204" t="n">
-        <v>7105633</v>
+        <v>7105643</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21704,10 +21695,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>126868551</v>
+        <v>126866155</v>
       </c>
       <c r="B205" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21715,37 +21706,37 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>678369</v>
+        <v>678318</v>
       </c>
       <c r="R205" t="n">
-        <v>7105652</v>
+        <v>7105498</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -21789,12 +21780,12 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
@@ -21805,45 +21796,45 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>126868616</v>
+        <v>126863395</v>
       </c>
       <c r="B206" t="n">
-        <v>80052</v>
+        <v>98443</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>678314</v>
+        <v>678285</v>
       </c>
       <c r="R206" t="n">
-        <v>7105567</v>
+        <v>7105493</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21890,12 +21881,12 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
@@ -21906,45 +21897,54 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>126868597</v>
+        <v>126861201</v>
       </c>
       <c r="B207" t="n">
-        <v>78772</v>
+        <v>98443</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>678369</v>
+        <v>678275</v>
       </c>
       <c r="R207" t="n">
-        <v>7105652</v>
+        <v>7105633</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21991,12 +21991,12 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
@@ -22007,10 +22007,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>126862276</v>
+        <v>126861171</v>
       </c>
       <c r="B208" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22018,37 +22018,37 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>678612</v>
+        <v>678240</v>
       </c>
       <c r="R208" t="n">
-        <v>7105680</v>
+        <v>7105621</v>
       </c>
       <c r="S208" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22080,37 +22080,35 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>Med apothecier.</t>
-        </is>
-      </c>
       <c r="AD208" t="b">
         <v>0</v>
       </c>
       <c r="AE208" t="b">
         <v>0</v>
       </c>
-      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY208" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>126861257</v>
+        <v>126862276</v>
       </c>
       <c r="B209" t="n">
         <v>79014</v>
@@ -22141,17 +22139,17 @@
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>678409</v>
+        <v>678612</v>
       </c>
       <c r="R209" t="n">
-        <v>7105692</v>
+        <v>7105680</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22183,35 +22181,37 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Med apothecier.</t>
+        </is>
+      </c>
       <c r="AD209" t="b">
         <v>0</v>
       </c>
       <c r="AE209" t="b">
         <v>0</v>
       </c>
+      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY209" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>126862285</v>
+        <v>126861257</v>
       </c>
       <c r="B210" t="n">
         <v>79014</v>
@@ -22242,17 +22242,17 @@
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>678540</v>
+        <v>678409</v>
       </c>
       <c r="R210" t="n">
-        <v>7105640</v>
+        <v>7105692</v>
       </c>
       <c r="S210" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -22296,22 +22296,26 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY210" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>126861171</v>
+        <v>126862285</v>
       </c>
       <c r="B211" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22319,37 +22323,37 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>678240</v>
+        <v>678540</v>
       </c>
       <c r="R211" t="n">
-        <v>7105621</v>
+        <v>7105640</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -22393,48 +22397,44 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY211" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>126866024</v>
+        <v>126865855</v>
       </c>
       <c r="B212" t="n">
-        <v>80145</v>
+        <v>91326</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22447,10 +22447,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>678594</v>
+        <v>678579</v>
       </c>
       <c r="R212" t="n">
-        <v>7105682</v>
+        <v>7105578</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22514,32 +22514,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>126865855</v>
+        <v>126866024</v>
       </c>
       <c r="B213" t="n">
-        <v>91326</v>
+        <v>80145</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22552,10 +22552,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>678579</v>
+        <v>678594</v>
       </c>
       <c r="R213" t="n">
-        <v>7105578</v>
+        <v>7105682</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22829,10 +22829,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>126865787</v>
+        <v>126865945</v>
       </c>
       <c r="B216" t="n">
-        <v>78420</v>
+        <v>79046</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22840,25 +22840,33 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6437</v>
+        <v>185</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
@@ -22867,10 +22875,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>678587</v>
+        <v>678604</v>
       </c>
       <c r="R216" t="n">
-        <v>7105527</v>
+        <v>7105685</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22934,10 +22942,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>126865945</v>
+        <v>126865787</v>
       </c>
       <c r="B217" t="n">
-        <v>79046</v>
+        <v>78420</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22945,33 +22953,25 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>185</v>
+        <v>6437</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
@@ -22980,10 +22980,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>678604</v>
+        <v>678587</v>
       </c>
       <c r="R217" t="n">
-        <v>7105685</v>
+        <v>7105527</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23888,10 +23888,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>126865445</v>
+        <v>126865442</v>
       </c>
       <c r="B226" t="n">
-        <v>80117</v>
+        <v>78773</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23899,21 +23899,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23923,10 +23923,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>678319</v>
+        <v>678295</v>
       </c>
       <c r="R226" t="n">
-        <v>7105572</v>
+        <v>7105600</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23989,10 +23989,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>126865442</v>
+        <v>126865445</v>
       </c>
       <c r="B227" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24000,21 +24000,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24024,10 +24024,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>678295</v>
+        <v>678319</v>
       </c>
       <c r="R227" t="n">
-        <v>7105600</v>
+        <v>7105572</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -914,51 +914,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126814991</v>
+        <v>126811416</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Råtjärnen, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>678395</v>
+        <v>678291</v>
       </c>
       <c r="R4" t="n">
         <v>7105492</v>
@@ -1008,54 +999,63 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126811416</v>
+        <v>126814991</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>678291</v>
+        <v>678395</v>
       </c>
       <c r="R5" t="n">
         <v>7105492</v>
@@ -1105,12 +1105,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1311,54 +1311,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814992</v>
+        <v>126811407</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Råtjärnen, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>678336</v>
+        <v>678303</v>
       </c>
       <c r="R8" t="n">
-        <v>7105495</v>
+        <v>7105499</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,57 +1396,66 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126811407</v>
+        <v>126814992</v>
       </c>
       <c r="B9" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>678303</v>
+        <v>678336</v>
       </c>
       <c r="R9" t="n">
-        <v>7105499</v>
+        <v>7105495</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,22 +1502,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814999</v>
+        <v>126815009</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>678379</v>
+        <v>678404</v>
       </c>
       <c r="R10" t="n">
-        <v>7105495</v>
+        <v>7105442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126815000</v>
+        <v>126814999</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>678391</v>
+        <v>678379</v>
       </c>
       <c r="R11" t="n">
-        <v>7105482</v>
+        <v>7105495</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126815009</v>
+        <v>126815000</v>
       </c>
       <c r="B12" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1719,21 +1719,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>678404</v>
+        <v>678391</v>
       </c>
       <c r="R12" t="n">
-        <v>7105442</v>
+        <v>7105482</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -12361,10 +12361,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126868550</v>
+        <v>126865185</v>
       </c>
       <c r="B115" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12372,34 +12372,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>678293</v>
+        <v>678603</v>
       </c>
       <c r="R115" t="n">
-        <v>7105493</v>
+        <v>7105573</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12443,15 +12443,30 @@
       <c r="AG115" t="b">
         <v>0</v>
       </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12462,48 +12477,51 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126862267</v>
+        <v>126865226</v>
       </c>
       <c r="B116" t="n">
-        <v>80117</v>
+        <v>80146</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>678314</v>
+        <v>678313</v>
       </c>
       <c r="R116" t="n">
-        <v>7105563</v>
+        <v>7105600</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12541,66 +12559,67 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126865185</v>
+        <v>126862274</v>
       </c>
       <c r="B117" t="n">
-        <v>79014</v>
+        <v>58334</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>678603</v>
+        <v>678512</v>
       </c>
       <c r="R117" t="n">
-        <v>7105573</v>
+        <v>7105616</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12640,86 +12659,64 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126865226</v>
+        <v>126852438</v>
       </c>
       <c r="B118" t="n">
-        <v>80146</v>
+        <v>78773</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>678313</v>
+        <v>678438</v>
       </c>
       <c r="R118" t="n">
-        <v>7105600</v>
+        <v>7105684</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12746,40 +12743,53 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr"/>
+          <t>Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126853157</v>
+        <v>126865316</v>
       </c>
       <c r="B119" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12787,38 +12797,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>678507</v>
+        <v>678353</v>
       </c>
       <c r="R119" t="n">
-        <v>7105595</v>
+        <v>7105503</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12848,19 +12854,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12875,60 +12871,64 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr"/>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126862297</v>
+        <v>126868550</v>
       </c>
       <c r="B120" t="n">
-        <v>98360</v>
+        <v>79632</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>678417</v>
+        <v>678293</v>
       </c>
       <c r="R120" t="n">
-        <v>7105592</v>
+        <v>7105493</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12972,22 +12972,26 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr"/>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126852438</v>
+        <v>126862267</v>
       </c>
       <c r="B121" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12995,37 +12999,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>678438</v>
+        <v>678314</v>
       </c>
       <c r="R121" t="n">
-        <v>7105684</v>
+        <v>7105563</v>
       </c>
       <c r="S121" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13052,19 +13056,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13079,64 +13073,64 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126862274</v>
+        <v>126853157</v>
       </c>
       <c r="B122" t="n">
-        <v>58334</v>
+        <v>57817</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>678512</v>
+        <v>678507</v>
       </c>
       <c r="R122" t="n">
-        <v>7105616</v>
+        <v>7105595</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13163,9 +13157,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13180,44 +13184,44 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126865316</v>
+        <v>126862297</v>
       </c>
       <c r="B123" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13227,13 +13231,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>678353</v>
+        <v>678417</v>
       </c>
       <c r="R123" t="n">
-        <v>7105503</v>
+        <v>7105592</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13277,19 +13281,15 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14343,7 +14343,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126861138</v>
+        <v>126861137</v>
       </c>
       <c r="B134" t="n">
         <v>78773</v>
@@ -14378,10 +14378,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>678295</v>
+        <v>678270</v>
       </c>
       <c r="R134" t="n">
-        <v>7105595</v>
+        <v>7105627</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14444,10 +14444,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126861322</v>
+        <v>126861138</v>
       </c>
       <c r="B135" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14455,21 +14455,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14479,10 +14479,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>678224</v>
+        <v>678295</v>
       </c>
       <c r="R135" t="n">
-        <v>7105630</v>
+        <v>7105595</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14545,10 +14545,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126861262</v>
+        <v>126868588</v>
       </c>
       <c r="B136" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14556,21 +14556,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14580,10 +14580,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>678532</v>
+        <v>678330</v>
       </c>
       <c r="R136" t="n">
-        <v>7105725</v>
+        <v>7105451</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14630,12 +14630,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14646,7 +14646,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126861315</v>
+        <v>126862287</v>
       </c>
       <c r="B137" t="n">
         <v>79014</v>
@@ -14677,17 +14677,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>678354</v>
+        <v>678359</v>
       </c>
       <c r="R137" t="n">
-        <v>7105657</v>
+        <v>7105587</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14731,26 +14731,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY137" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126868588</v>
+        <v>126861322</v>
       </c>
       <c r="B138" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14758,21 +14754,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14782,10 +14778,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>678330</v>
+        <v>678224</v>
       </c>
       <c r="R138" t="n">
-        <v>7105451</v>
+        <v>7105630</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14832,12 +14828,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14848,48 +14844,48 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126862287</v>
+        <v>126861105</v>
       </c>
       <c r="B139" t="n">
-        <v>79014</v>
+        <v>80021</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>678359</v>
+        <v>678330</v>
       </c>
       <c r="R139" t="n">
-        <v>7105587</v>
+        <v>7105447</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14933,22 +14929,26 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126861105</v>
+        <v>126868617</v>
       </c>
       <c r="B140" t="n">
-        <v>80021</v>
+        <v>80052</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14956,21 +14956,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14980,10 +14980,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>678330</v>
+        <v>678328</v>
       </c>
       <c r="R140" t="n">
-        <v>7105447</v>
+        <v>7105581</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15030,12 +15030,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15046,32 +15046,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126868617</v>
+        <v>126861307</v>
       </c>
       <c r="B141" t="n">
-        <v>80052</v>
+        <v>79014</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15081,10 +15081,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>678328</v>
+        <v>678356</v>
       </c>
       <c r="R141" t="n">
-        <v>7105581</v>
+        <v>7105708</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15131,12 +15131,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15147,7 +15147,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126861307</v>
+        <v>126861309</v>
       </c>
       <c r="B142" t="n">
         <v>79014</v>
@@ -15182,10 +15182,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>678356</v>
+        <v>678368</v>
       </c>
       <c r="R142" t="n">
-        <v>7105708</v>
+        <v>7105697</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15248,7 +15248,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126861309</v>
+        <v>126861262</v>
       </c>
       <c r="B143" t="n">
         <v>79014</v>
@@ -15283,10 +15283,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>678368</v>
+        <v>678532</v>
       </c>
       <c r="R143" t="n">
-        <v>7105697</v>
+        <v>7105725</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15349,10 +15349,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126861137</v>
+        <v>126861315</v>
       </c>
       <c r="B144" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15360,21 +15360,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15384,10 +15384,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>678270</v>
+        <v>678354</v>
       </c>
       <c r="R144" t="n">
-        <v>7105627</v>
+        <v>7105657</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15450,10 +15450,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126868627</v>
+        <v>126853557</v>
       </c>
       <c r="B145" t="n">
-        <v>79990</v>
+        <v>98443</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15461,37 +15461,41 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>392</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Degel.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>678330</v>
+        <v>678466</v>
       </c>
       <c r="R145" t="n">
-        <v>7105453</v>
+        <v>7105581</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15518,9 +15522,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15535,12 +15549,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15551,10 +15565,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126861324</v>
+        <v>126865296</v>
       </c>
       <c r="B146" t="n">
-        <v>79014</v>
+        <v>41361</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15562,34 +15576,47 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>215713</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>678264</v>
+        <v>678332</v>
       </c>
       <c r="R146" t="n">
-        <v>7105625</v>
+        <v>7105461</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15636,12 +15663,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15652,48 +15679,48 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126868607</v>
+        <v>126862298</v>
       </c>
       <c r="B147" t="n">
-        <v>91344</v>
+        <v>98360</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>678439</v>
+        <v>678316</v>
       </c>
       <c r="R147" t="n">
-        <v>7105681</v>
+        <v>7105563</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15737,26 +15764,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY147" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126868596</v>
+        <v>126866154</v>
       </c>
       <c r="B148" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15764,37 +15787,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
         <v>678293</v>
       </c>
       <c r="R148" t="n">
-        <v>7105493</v>
+        <v>7105600</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15838,12 +15861,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -15854,48 +15877,48 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126851438</v>
+        <v>126868627</v>
       </c>
       <c r="B149" t="n">
-        <v>80117</v>
+        <v>79990</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>392</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>678352</v>
+        <v>678330</v>
       </c>
       <c r="R149" t="n">
-        <v>7105670</v>
+        <v>7105453</v>
       </c>
       <c r="S149" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15922,19 +15945,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>10:23</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15949,22 +15962,26 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr"/>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126865296</v>
+        <v>126861324</v>
       </c>
       <c r="B150" t="n">
-        <v>41361</v>
+        <v>79014</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15972,47 +15989,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>215713</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>678332</v>
+        <v>678264</v>
       </c>
       <c r="R150" t="n">
-        <v>7105461</v>
+        <v>7105625</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16059,12 +16063,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -16075,48 +16079,48 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126862298</v>
+        <v>126868607</v>
       </c>
       <c r="B151" t="n">
-        <v>98360</v>
+        <v>91344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>678316</v>
+        <v>678439</v>
       </c>
       <c r="R151" t="n">
-        <v>7105563</v>
+        <v>7105681</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16160,22 +16164,26 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr"/>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126866154</v>
+        <v>126868596</v>
       </c>
       <c r="B152" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16183,37 +16191,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
         <v>678293</v>
       </c>
       <c r="R152" t="n">
-        <v>7105600</v>
+        <v>7105493</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16257,12 +16265,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -16273,49 +16281,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126853557</v>
+        <v>126851438</v>
       </c>
       <c r="B153" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>678466</v>
+        <v>678352</v>
       </c>
       <c r="R153" t="n">
-        <v>7105581</v>
+        <v>7105670</v>
       </c>
       <c r="S153" t="n">
         <v>1</v>
@@ -16347,7 +16351,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16357,7 +16361,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16372,19 +16376,15 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY153" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -21186,45 +21186,49 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126868551</v>
+        <v>126868614</v>
       </c>
       <c r="B200" t="n">
-        <v>79632</v>
+        <v>98360</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>678369</v>
+        <v>678329</v>
       </c>
       <c r="R200" t="n">
-        <v>7105652</v>
+        <v>7105527</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21287,32 +21291,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>126868616</v>
+        <v>126861139</v>
       </c>
       <c r="B201" t="n">
-        <v>80052</v>
+        <v>78773</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6457</v>
+        <v>228912</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21322,10 +21326,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>678314</v>
+        <v>678244</v>
       </c>
       <c r="R201" t="n">
-        <v>7105567</v>
+        <v>7105643</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21372,12 +21376,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -21388,10 +21392,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>126868597</v>
+        <v>126866155</v>
       </c>
       <c r="B202" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21399,37 +21403,37 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>678369</v>
+        <v>678318</v>
       </c>
       <c r="R202" t="n">
-        <v>7105652</v>
+        <v>7105498</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21473,12 +21477,12 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -21489,49 +21493,45 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>126868614</v>
+        <v>126863395</v>
       </c>
       <c r="B203" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>678329</v>
+        <v>678285</v>
       </c>
       <c r="R203" t="n">
-        <v>7105527</v>
+        <v>7105493</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21578,12 +21578,12 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
@@ -21594,45 +21594,54 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>126861139</v>
+        <v>126861201</v>
       </c>
       <c r="B204" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>678244</v>
+        <v>678275</v>
       </c>
       <c r="R204" t="n">
-        <v>7105643</v>
+        <v>7105633</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21695,10 +21704,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>126866155</v>
+        <v>126868551</v>
       </c>
       <c r="B205" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21706,37 +21715,37 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>678318</v>
+        <v>678369</v>
       </c>
       <c r="R205" t="n">
-        <v>7105498</v>
+        <v>7105652</v>
       </c>
       <c r="S205" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -21780,12 +21789,12 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
@@ -21796,45 +21805,45 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>126863395</v>
+        <v>126868616</v>
       </c>
       <c r="B206" t="n">
-        <v>98443</v>
+        <v>80052</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>678285</v>
+        <v>678314</v>
       </c>
       <c r="R206" t="n">
-        <v>7105493</v>
+        <v>7105567</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21881,12 +21890,12 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
@@ -21897,54 +21906,45 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>126861201</v>
+        <v>126868597</v>
       </c>
       <c r="B207" t="n">
-        <v>98443</v>
+        <v>78772</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>678275</v>
+        <v>678369</v>
       </c>
       <c r="R207" t="n">
-        <v>7105633</v>
+        <v>7105652</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21991,12 +21991,12 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
@@ -22409,32 +22409,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>126865855</v>
+        <v>126866024</v>
       </c>
       <c r="B212" t="n">
-        <v>91326</v>
+        <v>80145</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22447,10 +22447,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>678579</v>
+        <v>678594</v>
       </c>
       <c r="R212" t="n">
-        <v>7105578</v>
+        <v>7105682</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22514,32 +22514,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>126866024</v>
+        <v>126865855</v>
       </c>
       <c r="B213" t="n">
-        <v>80145</v>
+        <v>91326</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22552,10 +22552,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>678594</v>
+        <v>678579</v>
       </c>
       <c r="R213" t="n">
-        <v>7105682</v>
+        <v>7105578</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22829,10 +22829,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>126865945</v>
+        <v>126865787</v>
       </c>
       <c r="B216" t="n">
-        <v>79046</v>
+        <v>78420</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22840,33 +22840,25 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>185</v>
+        <v>6437</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
@@ -22875,10 +22867,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>678604</v>
+        <v>678587</v>
       </c>
       <c r="R216" t="n">
-        <v>7105685</v>
+        <v>7105527</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22942,10 +22934,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>126865787</v>
+        <v>126865945</v>
       </c>
       <c r="B217" t="n">
-        <v>78420</v>
+        <v>79046</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22953,25 +22945,33 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6437</v>
+        <v>185</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
@@ -22980,10 +22980,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>678587</v>
+        <v>678604</v>
       </c>
       <c r="R217" t="n">
-        <v>7105527</v>
+        <v>7105685</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23047,10 +23047,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>126866090</v>
+        <v>126865996</v>
       </c>
       <c r="B218" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23058,43 +23058,26 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
@@ -23102,10 +23085,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>678594</v>
+        <v>678605</v>
       </c>
       <c r="R218" t="n">
-        <v>7105682</v>
+        <v>7105707</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23146,6 +23129,7 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
+      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
@@ -23157,7 +23141,7 @@
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Fredrik Wilde, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
@@ -23168,10 +23152,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>126865996</v>
+        <v>126866090</v>
       </c>
       <c r="B219" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23179,26 +23163,43 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
@@ -23206,10 +23207,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>678605</v>
+        <v>678594</v>
       </c>
       <c r="R219" t="n">
-        <v>7105707</v>
+        <v>7105682</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23250,7 +23251,6 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
-      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -23262,7 +23262,7 @@
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Fredrik Wilde, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
@@ -24090,32 +24090,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>126865443</v>
+        <v>126865431</v>
       </c>
       <c r="B228" t="n">
-        <v>78773</v>
+        <v>80042</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>228912</v>
+        <v>6003719</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Traslav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scytinium lichenoides</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -24125,10 +24125,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>678252</v>
+        <v>678319</v>
       </c>
       <c r="R228" t="n">
-        <v>7105495</v>
+        <v>7105574</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24191,32 +24191,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>126865431</v>
+        <v>126865443</v>
       </c>
       <c r="B229" t="n">
-        <v>80042</v>
+        <v>78773</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6003719</v>
+        <v>228912</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24226,10 +24226,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>678319</v>
+        <v>678252</v>
       </c>
       <c r="R229" t="n">
-        <v>7105574</v>
+        <v>7105495</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -1117,45 +1117,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814997</v>
+        <v>126811397</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råtjärnen, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>678319</v>
+        <v>678330</v>
       </c>
       <c r="R6" t="n">
-        <v>7105453</v>
+        <v>7105500</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,57 +1202,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126811397</v>
+        <v>126814997</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>678330</v>
+        <v>678319</v>
       </c>
       <c r="R7" t="n">
-        <v>7105500</v>
+        <v>7105453</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,66 +1299,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814992</v>
+        <v>126811407</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Råtjärnen, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>678336</v>
+        <v>678303</v>
       </c>
       <c r="R8" t="n">
-        <v>7105495</v>
+        <v>7105499</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,57 +1396,66 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126811407</v>
+        <v>126814992</v>
       </c>
       <c r="B9" t="n">
-        <v>98364</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>678303</v>
+        <v>678336</v>
       </c>
       <c r="R9" t="n">
-        <v>7105499</v>
+        <v>7105495</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,22 +1502,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126815009</v>
+        <v>126814999</v>
       </c>
       <c r="B10" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>678404</v>
+        <v>678379</v>
       </c>
       <c r="R10" t="n">
-        <v>7105442</v>
+        <v>7105495</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126814999</v>
+        <v>126815000</v>
       </c>
       <c r="B11" t="n">
         <v>79018</v>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>678379</v>
+        <v>678391</v>
       </c>
       <c r="R11" t="n">
-        <v>7105495</v>
+        <v>7105482</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126815000</v>
+        <v>126815009</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1719,21 +1719,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>678391</v>
+        <v>678404</v>
       </c>
       <c r="R12" t="n">
-        <v>7105482</v>
+        <v>7105442</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3253,48 +3253,51 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126862275</v>
+        <v>126865383</v>
       </c>
       <c r="B27" t="n">
-        <v>91491</v>
+        <v>92620</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>678635</v>
+        <v>678418</v>
       </c>
       <c r="R27" t="n">
-        <v>7105683</v>
+        <v>7105550</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3332,69 +3335,67 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126865383</v>
+        <v>126862275</v>
       </c>
       <c r="B28" t="n">
-        <v>92620</v>
+        <v>91491</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>678418</v>
+        <v>678635</v>
       </c>
       <c r="R28" t="n">
-        <v>7105550</v>
+        <v>7105683</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3432,19 +3433,18 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3650,45 +3650,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126861256</v>
+        <v>126865250</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>678406</v>
+        <v>678332</v>
       </c>
       <c r="R31" t="n">
-        <v>7105684</v>
+        <v>7105584</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3732,15 +3732,30 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3751,45 +3766,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126865250</v>
+        <v>126861256</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>678332</v>
+        <v>678406</v>
       </c>
       <c r="R32" t="n">
-        <v>7105584</v>
+        <v>7105684</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3833,30 +3848,15 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -5219,45 +5219,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126865181</v>
+        <v>126861104</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>80025</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>678324</v>
+        <v>678269</v>
       </c>
       <c r="R46" t="n">
-        <v>7105598</v>
+        <v>7105603</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5301,30 +5301,15 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5335,10 +5320,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126862286</v>
+        <v>126865757</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5346,37 +5331,40 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>678452</v>
+        <v>678290</v>
       </c>
       <c r="R47" t="n">
-        <v>7105602</v>
+        <v>7105528</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5414,28 +5402,33 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Lotta Ihse</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126850977</v>
+        <v>126861056</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5443,37 +5436,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>678347</v>
+        <v>678315</v>
       </c>
       <c r="R48" t="n">
-        <v>7105602</v>
+        <v>7105477</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5500,19 +5493,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5527,12 +5510,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5543,48 +5526,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126866161</v>
+        <v>126865181</v>
       </c>
       <c r="B49" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>678315</v>
+        <v>678324</v>
       </c>
       <c r="R49" t="n">
-        <v>7105536</v>
+        <v>7105598</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5624,16 +5607,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5644,10 +5642,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126862265</v>
+        <v>126862286</v>
       </c>
       <c r="B50" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5655,21 +5653,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5679,10 +5677,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>678288</v>
+        <v>678452</v>
       </c>
       <c r="R50" t="n">
-        <v>7105530</v>
+        <v>7105602</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5741,10 +5739,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126865464</v>
+        <v>126850977</v>
       </c>
       <c r="B51" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5752,40 +5750,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>678496</v>
+        <v>678347</v>
       </c>
       <c r="R51" t="n">
-        <v>7105543</v>
+        <v>7105602</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5812,78 +5807,91 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126861056</v>
+        <v>126866161</v>
       </c>
       <c r="B52" t="n">
-        <v>91330</v>
+        <v>98364</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
         <v>678315</v>
       </c>
       <c r="R52" t="n">
-        <v>7105477</v>
+        <v>7105536</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5927,12 +5935,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5943,48 +5951,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126861104</v>
+        <v>126862265</v>
       </c>
       <c r="B53" t="n">
-        <v>80025</v>
+        <v>78777</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>678269</v>
+        <v>678288</v>
       </c>
       <c r="R53" t="n">
-        <v>7105603</v>
+        <v>7105530</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6028,26 +6036,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126865757</v>
+        <v>126865464</v>
       </c>
       <c r="B54" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6055,21 +6059,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6082,10 +6086,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>678290</v>
+        <v>678496</v>
       </c>
       <c r="R54" t="n">
-        <v>7105528</v>
+        <v>7105543</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6133,19 +6137,15 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6356,10 +6356,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126865759</v>
+        <v>126868577</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>75137</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6367,37 +6367,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>678614</v>
+        <v>678313</v>
       </c>
       <c r="R57" t="n">
-        <v>7105648</v>
+        <v>7105562</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6438,19 +6435,18 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6461,48 +6457,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126851831</v>
+        <v>126866163</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>678360</v>
+        <v>678468</v>
       </c>
       <c r="R58" t="n">
-        <v>7105719</v>
+        <v>7105617</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6529,19 +6525,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:46</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:46</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6556,12 +6542,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6572,57 +6558,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126850880</v>
+        <v>126861170</v>
       </c>
       <c r="B59" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>678346</v>
+        <v>678251</v>
       </c>
       <c r="R59" t="n">
-        <v>7105594</v>
+        <v>7105649</v>
       </c>
       <c r="S59" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6649,19 +6626,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6676,12 +6643,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6692,52 +6659,51 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126860443</v>
+        <v>126865759</v>
       </c>
       <c r="B60" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>678344</v>
+        <v>678614</v>
       </c>
       <c r="R60" t="n">
-        <v>7105500</v>
+        <v>7105648</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6764,39 +6730,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6807,10 +6764,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126868577</v>
+        <v>126851831</v>
       </c>
       <c r="B61" t="n">
-        <v>75137</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6818,37 +6775,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>678313</v>
+        <v>678360</v>
       </c>
       <c r="R61" t="n">
-        <v>7105562</v>
+        <v>7105719</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6875,9 +6832,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6892,12 +6859,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6908,32 +6875,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126866163</v>
+        <v>126863389</v>
       </c>
       <c r="B62" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6943,13 +6910,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>678468</v>
+        <v>678532</v>
       </c>
       <c r="R62" t="n">
-        <v>7105617</v>
+        <v>7105778</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6993,12 +6960,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7009,48 +6976,57 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126861170</v>
+        <v>126850880</v>
       </c>
       <c r="B63" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>678251</v>
+        <v>678346</v>
       </c>
       <c r="R63" t="n">
-        <v>7105649</v>
+        <v>7105594</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7077,9 +7053,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7094,12 +7080,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7110,48 +7096,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126863389</v>
+        <v>126860443</v>
       </c>
       <c r="B64" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>678532</v>
+        <v>678344</v>
       </c>
       <c r="R64" t="n">
-        <v>7105778</v>
+        <v>7105500</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7178,9 +7168,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7195,12 +7195,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -8880,10 +8880,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126861212</v>
+        <v>126866144</v>
       </c>
       <c r="B81" t="n">
-        <v>91348</v>
+        <v>96700</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8891,37 +8891,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>678349</v>
+        <v>678308</v>
       </c>
       <c r="R81" t="n">
-        <v>7105698</v>
+        <v>7105565</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8965,12 +8965,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8981,10 +8981,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126862284</v>
+        <v>126861212</v>
       </c>
       <c r="B82" t="n">
-        <v>79018</v>
+        <v>91348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8992,37 +8992,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>678561</v>
+        <v>678349</v>
       </c>
       <c r="R82" t="n">
-        <v>7105684</v>
+        <v>7105698</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9066,19 +9066,23 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126861311</v>
+        <v>126862284</v>
       </c>
       <c r="B83" t="n">
         <v>79018</v>
@@ -9109,17 +9113,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>678389</v>
+        <v>678561</v>
       </c>
       <c r="R83" t="n">
-        <v>7105676</v>
+        <v>7105684</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9163,23 +9167,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126861316</v>
+        <v>126861311</v>
       </c>
       <c r="B84" t="n">
         <v>79018</v>
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>678325</v>
+        <v>678389</v>
       </c>
       <c r="R84" t="n">
-        <v>7105669</v>
+        <v>7105676</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9280,10 +9280,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126866144</v>
+        <v>126861316</v>
       </c>
       <c r="B85" t="n">
-        <v>96700</v>
+        <v>79018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9291,37 +9291,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>678308</v>
+        <v>678325</v>
       </c>
       <c r="R85" t="n">
-        <v>7105565</v>
+        <v>7105669</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9365,12 +9365,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9381,45 +9381,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126861046</v>
+        <v>126865255</v>
       </c>
       <c r="B86" t="n">
-        <v>79636</v>
+        <v>98365</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>223591</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>678285</v>
+        <v>678327</v>
       </c>
       <c r="R86" t="n">
-        <v>7105527</v>
+        <v>7105520</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9466,12 +9466,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9482,32 +9482,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126861080</v>
+        <v>126861046</v>
       </c>
       <c r="B87" t="n">
-        <v>80150</v>
+        <v>79636</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9517,10 +9517,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>678337</v>
+        <v>678285</v>
       </c>
       <c r="R87" t="n">
-        <v>7105676</v>
+        <v>7105527</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9583,48 +9583,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126862249</v>
+        <v>126861080</v>
       </c>
       <c r="B88" t="n">
-        <v>57821</v>
+        <v>80150</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>678565</v>
+        <v>678337</v>
       </c>
       <c r="R88" t="n">
-        <v>7105751</v>
+        <v>7105676</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9668,44 +9668,48 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126865255</v>
+        <v>126862249</v>
       </c>
       <c r="B89" t="n">
-        <v>98365</v>
+        <v>57821</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>223591</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9715,13 +9719,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>678327</v>
+        <v>678565</v>
       </c>
       <c r="R89" t="n">
-        <v>7105520</v>
+        <v>7105751</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9765,19 +9769,15 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -12361,51 +12361,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126865226</v>
+        <v>126852438</v>
       </c>
       <c r="B115" t="n">
-        <v>80150</v>
+        <v>78777</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>678313</v>
+        <v>678438</v>
       </c>
       <c r="R115" t="n">
-        <v>7105600</v>
+        <v>7105684</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12432,40 +12429,53 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
+          <t>Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126868550</v>
+        <v>126865316</v>
       </c>
       <c r="B116" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12473,34 +12483,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>678293</v>
+        <v>678353</v>
       </c>
       <c r="R116" t="n">
-        <v>7105493</v>
+        <v>7105503</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12547,12 +12557,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12563,10 +12573,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126862267</v>
+        <v>126865185</v>
       </c>
       <c r="B117" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12574,37 +12584,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>678314</v>
+        <v>678603</v>
       </c>
       <c r="R117" t="n">
-        <v>7105563</v>
+        <v>7105573</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12644,48 +12654,67 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr"/>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126865316</v>
+        <v>126862297</v>
       </c>
       <c r="B118" t="n">
-        <v>79018</v>
+        <v>98364</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12695,13 +12724,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>678353</v>
+        <v>678417</v>
       </c>
       <c r="R118" t="n">
-        <v>7105503</v>
+        <v>7105592</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12745,26 +12774,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126865185</v>
+        <v>126853157</v>
       </c>
       <c r="B119" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12772,34 +12797,38 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>678603</v>
+        <v>678507</v>
       </c>
       <c r="R119" t="n">
-        <v>7105573</v>
+        <v>7105595</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12829,11 +12858,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -12842,45 +12881,26 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126862274</v>
+        <v>126865226</v>
       </c>
       <c r="B120" t="n">
-        <v>58338</v>
+        <v>80150</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12888,37 +12908,40 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>103044</v>
+        <v>6462</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>678512</v>
+        <v>678313</v>
       </c>
       <c r="R120" t="n">
-        <v>7105616</v>
+        <v>7105600</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12956,66 +12979,67 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126862297</v>
+        <v>126868550</v>
       </c>
       <c r="B121" t="n">
-        <v>98364</v>
+        <v>79636</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>678417</v>
+        <v>678293</v>
       </c>
       <c r="R121" t="n">
-        <v>7105592</v>
+        <v>7105493</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13059,22 +13083,26 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr"/>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126852438</v>
+        <v>126862267</v>
       </c>
       <c r="B122" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13082,37 +13110,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>678438</v>
+        <v>678314</v>
       </c>
       <c r="R122" t="n">
-        <v>7105684</v>
+        <v>7105563</v>
       </c>
       <c r="S122" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13139,19 +13167,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13166,68 +13184,60 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY122" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126853157</v>
+        <v>126862274</v>
       </c>
       <c r="B123" t="n">
-        <v>57821</v>
+        <v>58338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>678507</v>
+        <v>678512</v>
       </c>
       <c r="R123" t="n">
-        <v>7105595</v>
+        <v>7105616</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13254,19 +13264,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13281,57 +13281,57 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126865184</v>
+        <v>126861336</v>
       </c>
       <c r="B124" t="n">
-        <v>92813</v>
+        <v>98364</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2079</v>
+        <v>219790</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>678549</v>
+        <v>678246</v>
       </c>
       <c r="R124" t="n">
-        <v>7105535</v>
+        <v>7105631</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13375,30 +13375,15 @@
       <c r="AG124" t="b">
         <v>0</v>
       </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13409,45 +13394,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126868618</v>
+        <v>126865184</v>
       </c>
       <c r="B125" t="n">
-        <v>80056</v>
+        <v>92813</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6457</v>
+        <v>2079</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>678324</v>
+        <v>678549</v>
       </c>
       <c r="R125" t="n">
-        <v>7105582</v>
+        <v>7105535</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13491,15 +13476,30 @@
       <c r="AG125" t="b">
         <v>0</v>
       </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13510,32 +13510,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126868552</v>
+        <v>126868618</v>
       </c>
       <c r="B126" t="n">
-        <v>79636</v>
+        <v>80056</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6457</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13545,10 +13545,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>678377</v>
+        <v>678324</v>
       </c>
       <c r="R126" t="n">
-        <v>7105670</v>
+        <v>7105582</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13611,10 +13611,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126861167</v>
+        <v>126868552</v>
       </c>
       <c r="B127" t="n">
-        <v>80121</v>
+        <v>79636</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13622,21 +13622,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>678298</v>
+        <v>678377</v>
       </c>
       <c r="R127" t="n">
-        <v>7105658</v>
+        <v>7105670</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13696,12 +13696,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13712,32 +13712,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126861079</v>
+        <v>126861167</v>
       </c>
       <c r="B128" t="n">
-        <v>80150</v>
+        <v>80121</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13747,10 +13747,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>678363</v>
+        <v>678298</v>
       </c>
       <c r="R128" t="n">
-        <v>7105711</v>
+        <v>7105658</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13813,7 +13813,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126865251</v>
+        <v>126861079</v>
       </c>
       <c r="B129" t="n">
         <v>80150</v>
@@ -13844,14 +13844,14 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>678319</v>
+        <v>678363</v>
       </c>
       <c r="R129" t="n">
-        <v>7105574</v>
+        <v>7105711</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13895,30 +13895,15 @@
       <c r="AG129" t="b">
         <v>0</v>
       </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -13929,45 +13914,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126861263</v>
+        <v>126865251</v>
       </c>
       <c r="B130" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>678535</v>
+        <v>678319</v>
       </c>
       <c r="R130" t="n">
-        <v>7105767</v>
+        <v>7105574</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14011,15 +13996,30 @@
       <c r="AG130" t="b">
         <v>0</v>
       </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14030,7 +14030,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126868610</v>
+        <v>126861263</v>
       </c>
       <c r="B131" t="n">
         <v>79018</v>
@@ -14065,10 +14065,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>678379</v>
+        <v>678535</v>
       </c>
       <c r="R131" t="n">
-        <v>7105668</v>
+        <v>7105767</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14115,12 +14115,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14131,32 +14131,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126861336</v>
+        <v>126868610</v>
       </c>
       <c r="B132" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14166,10 +14166,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>678246</v>
+        <v>678379</v>
       </c>
       <c r="R132" t="n">
-        <v>7105631</v>
+        <v>7105668</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14216,12 +14216,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -16388,10 +16388,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126865776</v>
+        <v>126865272</v>
       </c>
       <c r="B154" t="n">
-        <v>79607</v>
+        <v>91330</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16399,21 +16399,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16426,10 +16426,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>678531</v>
+        <v>678324</v>
       </c>
       <c r="R154" t="n">
-        <v>7105530</v>
+        <v>7105605</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16485,56 +16485,52 @@
           <t>Fredrik Wilde</t>
         </is>
       </c>
-      <c r="AY154" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+      <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126861112</v>
+        <v>126860442</v>
       </c>
       <c r="B155" t="n">
-        <v>97325</v>
+        <v>79018</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>678264</v>
+        <v>678328</v>
       </c>
       <c r="R155" t="n">
-        <v>7105660</v>
+        <v>7105453</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16561,9 +16557,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16578,12 +16584,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -16594,10 +16600,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126865272</v>
+        <v>126865310</v>
       </c>
       <c r="B156" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16605,37 +16611,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>678324</v>
+        <v>678503</v>
       </c>
       <c r="R156" t="n">
-        <v>7105605</v>
+        <v>7105771</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16676,64 +16679,67 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr"/>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126865178</v>
+        <v>126861318</v>
       </c>
       <c r="B157" t="n">
-        <v>80025</v>
+        <v>79018</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>678296</v>
+        <v>678328</v>
       </c>
       <c r="R157" t="n">
-        <v>7105501</v>
+        <v>7105677</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16777,30 +16783,15 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -16811,48 +16802,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126865103</v>
+        <v>126865178</v>
       </c>
       <c r="B158" t="n">
-        <v>80121</v>
+        <v>80025</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>678320</v>
+        <v>678296</v>
       </c>
       <c r="R158" t="n">
-        <v>7105573</v>
+        <v>7105501</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16893,29 +16881,47 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr"/>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126860442</v>
+        <v>126865103</v>
       </c>
       <c r="B159" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16923,37 +16929,40 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>678328</v>
+        <v>678320</v>
       </c>
       <c r="R159" t="n">
-        <v>7105453</v>
+        <v>7105573</v>
       </c>
       <c r="S159" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16980,53 +16989,40 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY159" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126865310</v>
+        <v>126861057</v>
       </c>
       <c r="B160" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17034,34 +17030,48 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>678503</v>
+        <v>678394</v>
       </c>
       <c r="R160" t="n">
-        <v>7105771</v>
+        <v>7105671</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17108,12 +17118,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -17124,10 +17134,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126861318</v>
+        <v>126865776</v>
       </c>
       <c r="B161" t="n">
-        <v>79018</v>
+        <v>79607</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17135,34 +17145,37 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>678328</v>
+        <v>678531</v>
       </c>
       <c r="R161" t="n">
-        <v>7105677</v>
+        <v>7105530</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17203,18 +17216,19 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -17225,59 +17239,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126861057</v>
+        <v>126861112</v>
       </c>
       <c r="B162" t="n">
-        <v>57661</v>
+        <v>97325</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>678394</v>
+        <v>678264</v>
       </c>
       <c r="R162" t="n">
-        <v>7105671</v>
+        <v>7105660</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19830,10 +19830,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>126865763</v>
+        <v>126861173</v>
       </c>
       <c r="B187" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19841,37 +19841,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>678314</v>
+        <v>678296</v>
       </c>
       <c r="R187" t="n">
-        <v>7105612</v>
+        <v>7105491</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19912,19 +19909,18 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
-      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -20234,10 +20230,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>126865182</v>
+        <v>126861048</v>
       </c>
       <c r="B191" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20245,34 +20241,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>678390</v>
+        <v>678521</v>
       </c>
       <c r="R191" t="n">
-        <v>7105570</v>
+        <v>7105765</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20316,30 +20312,15 @@
       <c r="AG191" t="b">
         <v>0</v>
       </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO191" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -20350,10 +20331,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>126861261</v>
+        <v>126865183</v>
       </c>
       <c r="B192" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20361,34 +20342,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>678484</v>
+        <v>678508</v>
       </c>
       <c r="R192" t="n">
-        <v>7105705</v>
+        <v>7105521</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20432,15 +20413,30 @@
       <c r="AG192" t="b">
         <v>0</v>
       </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -20451,7 +20447,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126861326</v>
+        <v>126865763</v>
       </c>
       <c r="B193" t="n">
         <v>79018</v>
@@ -20480,16 +20476,19 @@
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>678283</v>
+        <v>678314</v>
       </c>
       <c r="R193" t="n">
-        <v>7105602</v>
+        <v>7105612</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20530,18 +20529,19 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -20552,10 +20552,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126861048</v>
+        <v>126865182</v>
       </c>
       <c r="B194" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20563,34 +20563,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>678521</v>
+        <v>678390</v>
       </c>
       <c r="R194" t="n">
-        <v>7105765</v>
+        <v>7105570</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20634,15 +20634,30 @@
       <c r="AG194" t="b">
         <v>0</v>
       </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -20653,10 +20668,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126865183</v>
+        <v>126861261</v>
       </c>
       <c r="B195" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20664,34 +20679,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>678508</v>
+        <v>678484</v>
       </c>
       <c r="R195" t="n">
-        <v>7105521</v>
+        <v>7105705</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20735,30 +20750,15 @@
       <c r="AG195" t="b">
         <v>0</v>
       </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO195" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -20769,10 +20769,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126861173</v>
+        <v>126861326</v>
       </c>
       <c r="B196" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20780,21 +20780,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20804,10 +20804,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>678296</v>
+        <v>678283</v>
       </c>
       <c r="R196" t="n">
-        <v>7105491</v>
+        <v>7105602</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22007,10 +22007,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>126861171</v>
+        <v>126862276</v>
       </c>
       <c r="B208" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22018,37 +22018,37 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>678240</v>
+        <v>678612</v>
       </c>
       <c r="R208" t="n">
-        <v>7105621</v>
+        <v>7105680</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22080,38 +22080,40 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>Med apothecier.</t>
+        </is>
+      </c>
       <c r="AD208" t="b">
         <v>0</v>
       </c>
       <c r="AE208" t="b">
         <v>0</v>
       </c>
+      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY208" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>126862285</v>
+        <v>126861171</v>
       </c>
       <c r="B209" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22119,37 +22121,37 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>678540</v>
+        <v>678240</v>
       </c>
       <c r="R209" t="n">
-        <v>7105640</v>
+        <v>7105621</v>
       </c>
       <c r="S209" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22193,19 +22195,23 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY209" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>126861257</v>
+        <v>126862285</v>
       </c>
       <c r="B210" t="n">
         <v>79018</v>
@@ -22236,17 +22242,17 @@
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>678409</v>
+        <v>678540</v>
       </c>
       <c r="R210" t="n">
-        <v>7105692</v>
+        <v>7105640</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -22290,23 +22296,19 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY210" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>126862276</v>
+        <v>126861257</v>
       </c>
       <c r="B211" t="n">
         <v>79018</v>
@@ -22337,17 +22339,17 @@
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>678612</v>
+        <v>678409</v>
       </c>
       <c r="R211" t="n">
-        <v>7105680</v>
+        <v>7105692</v>
       </c>
       <c r="S211" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -22379,33 +22381,31 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Med apothecier.</t>
-        </is>
-      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY211" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -1514,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814999</v>
+        <v>126815009</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>678379</v>
+        <v>678404</v>
       </c>
       <c r="R10" t="n">
-        <v>7105495</v>
+        <v>7105442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126815000</v>
+        <v>126814999</v>
       </c>
       <c r="B11" t="n">
         <v>79018</v>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>678391</v>
+        <v>678379</v>
       </c>
       <c r="R11" t="n">
-        <v>7105482</v>
+        <v>7105495</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126815009</v>
+        <v>126815000</v>
       </c>
       <c r="B12" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1719,21 +1719,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>678404</v>
+        <v>678391</v>
       </c>
       <c r="R12" t="n">
-        <v>7105442</v>
+        <v>7105482</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2507,48 +2507,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126860448</v>
+        <v>126861081</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>678446</v>
+        <v>678254</v>
       </c>
       <c r="R20" t="n">
-        <v>7105699</v>
+        <v>7105631</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2575,19 +2575,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2602,12 +2592,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2618,32 +2608,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126861081</v>
+        <v>126861142</v>
       </c>
       <c r="B21" t="n">
-        <v>80150</v>
+        <v>80121</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>678254</v>
+        <v>678244</v>
       </c>
       <c r="R21" t="n">
-        <v>7105631</v>
+        <v>7105642</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,6 +2679,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2719,45 +2714,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126861142</v>
+        <v>126861202</v>
       </c>
       <c r="B22" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>678244</v>
+        <v>678291</v>
       </c>
       <c r="R22" t="n">
-        <v>7105642</v>
+        <v>7105551</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,11 +2794,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2825,10 +2824,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126865187</v>
+        <v>126860448</v>
       </c>
       <c r="B23" t="n">
-        <v>78424</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2836,37 +2835,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>678622</v>
+        <v>678446</v>
       </c>
       <c r="R23" t="n">
-        <v>7105605</v>
+        <v>7105699</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2893,11 +2892,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2906,31 +2915,16 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2941,10 +2935,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126861312</v>
+        <v>126865187</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>78424</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,34 +2946,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>678383</v>
+        <v>678622</v>
       </c>
       <c r="R24" t="n">
-        <v>7105668</v>
+        <v>7105605</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,15 +3017,30 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3042,7 +3051,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126861260</v>
+        <v>126861312</v>
       </c>
       <c r="B25" t="n">
         <v>79018</v>
@@ -3077,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>678449</v>
+        <v>678383</v>
       </c>
       <c r="R25" t="n">
-        <v>7105699</v>
+        <v>7105668</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,54 +3152,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126861202</v>
+        <v>126861260</v>
       </c>
       <c r="B26" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>678291</v>
+        <v>678449</v>
       </c>
       <c r="R26" t="n">
-        <v>7105551</v>
+        <v>7105699</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4184,45 +4184,59 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126868575</v>
+        <v>126861190</v>
       </c>
       <c r="B36" t="n">
-        <v>75137</v>
+        <v>98447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>310</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>678314</v>
+        <v>678394</v>
       </c>
       <c r="R36" t="n">
-        <v>7105563</v>
+        <v>7105687</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4269,12 +4283,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4285,48 +4299,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126862248</v>
+        <v>126868575</v>
       </c>
       <c r="B37" t="n">
-        <v>91740</v>
+        <v>75137</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4217</v>
+        <v>310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>678320</v>
+        <v>678314</v>
       </c>
       <c r="R37" t="n">
-        <v>7105489</v>
+        <v>7105563</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4370,60 +4384,64 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126861174</v>
+        <v>126862248</v>
       </c>
       <c r="B38" t="n">
-        <v>80121</v>
+        <v>91740</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>4217</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>678325</v>
+        <v>678320</v>
       </c>
       <c r="R38" t="n">
-        <v>7105453</v>
+        <v>7105489</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4467,26 +4485,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126861189</v>
+        <v>126861174</v>
       </c>
       <c r="B39" t="n">
-        <v>78776</v>
+        <v>80121</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4494,21 +4508,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4518,10 +4532,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>678292</v>
+        <v>678325</v>
       </c>
       <c r="R39" t="n">
-        <v>7105494</v>
+        <v>7105453</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,10 +4598,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126861168</v>
+        <v>126861189</v>
       </c>
       <c r="B40" t="n">
-        <v>80121</v>
+        <v>78776</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4595,21 +4609,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4619,10 +4633,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>678283</v>
+        <v>678292</v>
       </c>
       <c r="R40" t="n">
-        <v>7105656</v>
+        <v>7105494</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4685,48 +4699,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126865003</v>
+        <v>126861168</v>
       </c>
       <c r="B41" t="n">
-        <v>80150</v>
+        <v>80121</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>678319</v>
+        <v>678283</v>
       </c>
       <c r="R41" t="n">
-        <v>7105555</v>
+        <v>7105656</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4767,29 +4778,32 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126868625</v>
+        <v>126865003</v>
       </c>
       <c r="B42" t="n">
-        <v>80156</v>
+        <v>80150</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4797,34 +4811,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>678364</v>
+        <v>678319</v>
       </c>
       <c r="R42" t="n">
-        <v>7105634</v>
+        <v>7105555</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4865,49 +4882,46 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126865315</v>
+        <v>126868625</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>80156</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4918,14 +4932,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>678348</v>
+        <v>678364</v>
       </c>
       <c r="R43" t="n">
-        <v>7105510</v>
+        <v>7105634</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4972,12 +4986,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4988,59 +5002,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126861190</v>
+        <v>126865315</v>
       </c>
       <c r="B44" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>678394</v>
+        <v>678348</v>
       </c>
       <c r="R44" t="n">
-        <v>7105687</v>
+        <v>7105510</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5087,12 +5087,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5219,45 +5219,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126861104</v>
+        <v>126865181</v>
       </c>
       <c r="B46" t="n">
-        <v>80025</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>678269</v>
+        <v>678324</v>
       </c>
       <c r="R46" t="n">
-        <v>7105603</v>
+        <v>7105598</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5301,15 +5301,30 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5320,10 +5335,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126865757</v>
+        <v>126862286</v>
       </c>
       <c r="B47" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5331,40 +5346,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>678290</v>
+        <v>678452</v>
       </c>
       <c r="R47" t="n">
-        <v>7105528</v>
+        <v>7105602</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5402,33 +5414,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126861056</v>
+        <v>126850977</v>
       </c>
       <c r="B48" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5436,37 +5443,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>678315</v>
+        <v>678347</v>
       </c>
       <c r="R48" t="n">
-        <v>7105477</v>
+        <v>7105602</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5493,9 +5500,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5510,12 +5527,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5526,48 +5543,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126865181</v>
+        <v>126866161</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>98364</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>678324</v>
+        <v>678315</v>
       </c>
       <c r="R49" t="n">
-        <v>7105598</v>
+        <v>7105536</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5607,31 +5624,16 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5642,10 +5644,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126862286</v>
+        <v>126862265</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5653,21 +5655,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5677,10 +5679,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>678452</v>
+        <v>678288</v>
       </c>
       <c r="R50" t="n">
-        <v>7105602</v>
+        <v>7105530</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5739,10 +5741,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126850977</v>
+        <v>126865464</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5750,37 +5752,40 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>678347</v>
+        <v>678496</v>
       </c>
       <c r="R51" t="n">
-        <v>7105602</v>
+        <v>7105543</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5807,91 +5812,78 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126866161</v>
+        <v>126861056</v>
       </c>
       <c r="B52" t="n">
-        <v>98364</v>
+        <v>91330</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
         <v>678315</v>
       </c>
       <c r="R52" t="n">
-        <v>7105536</v>
+        <v>7105477</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5935,12 +5927,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5951,48 +5943,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126862265</v>
+        <v>126861104</v>
       </c>
       <c r="B53" t="n">
-        <v>78777</v>
+        <v>80025</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>678288</v>
+        <v>678269</v>
       </c>
       <c r="R53" t="n">
-        <v>7105530</v>
+        <v>7105603</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6036,22 +6028,26 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126865464</v>
+        <v>126865757</v>
       </c>
       <c r="B54" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6059,21 +6055,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6086,10 +6082,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>678496</v>
+        <v>678290</v>
       </c>
       <c r="R54" t="n">
-        <v>7105543</v>
+        <v>7105528</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6137,15 +6133,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Lotta Ihse</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7506,10 +7506,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126861165</v>
+        <v>126865314</v>
       </c>
       <c r="B68" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7517,34 +7517,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>678337</v>
+        <v>678506</v>
       </c>
       <c r="R68" t="n">
-        <v>7105669</v>
+        <v>7105716</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7591,12 +7591,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7607,32 +7607,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126861100</v>
+        <v>126868541</v>
       </c>
       <c r="B69" t="n">
-        <v>80025</v>
+        <v>75142</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>678335</v>
+        <v>678322</v>
       </c>
       <c r="R69" t="n">
-        <v>7105661</v>
+        <v>7105557</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7692,12 +7692,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7708,10 +7708,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126860445</v>
+        <v>126864836</v>
       </c>
       <c r="B70" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7719,34 +7719,45 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>678290</v>
+        <v>678301</v>
       </c>
       <c r="R70" t="n">
-        <v>7105581</v>
+        <v>7105516</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7776,53 +7787,40 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126865314</v>
+        <v>126856160</v>
       </c>
       <c r="B71" t="n">
-        <v>79018</v>
+        <v>78424</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7830,37 +7828,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>678506</v>
+        <v>678553</v>
       </c>
       <c r="R71" t="n">
-        <v>7105716</v>
+        <v>7105588</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7887,9 +7885,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7904,12 +7912,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7920,10 +7928,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126868541</v>
+        <v>126860445</v>
       </c>
       <c r="B72" t="n">
-        <v>75142</v>
+        <v>80121</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7931,34 +7939,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>678322</v>
+        <v>678290</v>
       </c>
       <c r="R72" t="n">
-        <v>7105557</v>
+        <v>7105581</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7988,9 +7996,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8005,12 +8023,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8021,10 +8039,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126864836</v>
+        <v>126865754</v>
       </c>
       <c r="B73" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8032,33 +8050,25 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -8067,10 +8077,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>678301</v>
+        <v>678603</v>
       </c>
       <c r="R73" t="n">
-        <v>7105516</v>
+        <v>7105660</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8118,22 +8128,26 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
+          <t>Lotta Ihse, Mattias Dalkvist, Anne Siivola, Malin Löfgren, Philipp Weiss, Carl Jansson, Peder Winding, Martin Axegård, Fredrik Wilde, Vilhelm Kroon, Cajsa Björkén, Hedda Bring</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126856160</v>
+        <v>126863392</v>
       </c>
       <c r="B74" t="n">
-        <v>78424</v>
+        <v>78777</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8141,37 +8155,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>678553</v>
+        <v>678371</v>
       </c>
       <c r="R74" t="n">
-        <v>7105588</v>
+        <v>7105650</v>
       </c>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8198,19 +8212,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>13:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8225,12 +8229,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8241,62 +8245,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126853937</v>
+        <v>126868582</v>
       </c>
       <c r="B75" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>678352</v>
+        <v>678369</v>
       </c>
       <c r="R75" t="n">
-        <v>7105670</v>
+        <v>7105652</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8323,19 +8313,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:39</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8350,61 +8330,61 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126868599</v>
+        <v>126861113</v>
       </c>
       <c r="B76" t="n">
-        <v>98447</v>
+        <v>97325</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>678290</v>
+        <v>678242</v>
       </c>
       <c r="R76" t="n">
-        <v>7105494</v>
+        <v>7105626</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8439,11 +8419,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Delvis blommande, grovt uppskattat antal</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8456,12 +8431,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8472,10 +8447,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126865754</v>
+        <v>126861165</v>
       </c>
       <c r="B77" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8483,37 +8458,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>678603</v>
+        <v>678337</v>
       </c>
       <c r="R77" t="n">
-        <v>7105660</v>
+        <v>7105669</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8554,19 +8526,18 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Mattias Dalkvist, Anne Siivola, Malin Löfgren, Philipp Weiss, Carl Jansson, Peder Winding, Martin Axegård, Fredrik Wilde, Vilhelm Kroon, Cajsa Björkén, Hedda Bring</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8577,45 +8548,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126863392</v>
+        <v>126861100</v>
       </c>
       <c r="B78" t="n">
-        <v>78777</v>
+        <v>80025</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>678371</v>
+        <v>678335</v>
       </c>
       <c r="R78" t="n">
-        <v>7105650</v>
+        <v>7105661</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8662,12 +8633,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8678,48 +8649,62 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126868582</v>
+        <v>126853937</v>
       </c>
       <c r="B79" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>678369</v>
+        <v>678352</v>
       </c>
       <c r="R79" t="n">
-        <v>7105652</v>
+        <v>7105670</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8746,9 +8731,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8763,61 +8758,61 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126861113</v>
+        <v>126868599</v>
       </c>
       <c r="B80" t="n">
-        <v>97325</v>
+        <v>98447</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>678242</v>
+        <v>678290</v>
       </c>
       <c r="R80" t="n">
-        <v>7105626</v>
+        <v>7105494</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8852,6 +8847,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Delvis blommande, grovt uppskattat antal</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8864,12 +8864,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8880,10 +8880,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126866144</v>
+        <v>126861212</v>
       </c>
       <c r="B81" t="n">
-        <v>96700</v>
+        <v>91348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8891,37 +8891,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>678308</v>
+        <v>678349</v>
       </c>
       <c r="R81" t="n">
-        <v>7105565</v>
+        <v>7105698</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8965,12 +8965,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8981,10 +8981,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126861212</v>
+        <v>126862284</v>
       </c>
       <c r="B82" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8992,37 +8992,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>678349</v>
+        <v>678561</v>
       </c>
       <c r="R82" t="n">
-        <v>7105698</v>
+        <v>7105684</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9066,23 +9066,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126862284</v>
+        <v>126861311</v>
       </c>
       <c r="B83" t="n">
         <v>79018</v>
@@ -9113,17 +9109,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>678561</v>
+        <v>678389</v>
       </c>
       <c r="R83" t="n">
-        <v>7105684</v>
+        <v>7105676</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9167,19 +9163,23 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126861311</v>
+        <v>126861316</v>
       </c>
       <c r="B84" t="n">
         <v>79018</v>
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>678389</v>
+        <v>678325</v>
       </c>
       <c r="R84" t="n">
-        <v>7105676</v>
+        <v>7105669</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9280,10 +9280,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126861316</v>
+        <v>126866144</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>96700</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9291,37 +9291,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>678325</v>
+        <v>678308</v>
       </c>
       <c r="R85" t="n">
-        <v>7105669</v>
+        <v>7105565</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9365,12 +9365,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9381,45 +9381,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126865255</v>
+        <v>126861046</v>
       </c>
       <c r="B86" t="n">
-        <v>98365</v>
+        <v>79636</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>223591</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>678327</v>
+        <v>678285</v>
       </c>
       <c r="R86" t="n">
-        <v>7105520</v>
+        <v>7105527</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9466,12 +9466,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9482,32 +9482,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126861046</v>
+        <v>126861080</v>
       </c>
       <c r="B87" t="n">
-        <v>79636</v>
+        <v>80150</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9517,10 +9517,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>678285</v>
+        <v>678337</v>
       </c>
       <c r="R87" t="n">
-        <v>7105527</v>
+        <v>7105676</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9583,48 +9583,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126861080</v>
+        <v>126862249</v>
       </c>
       <c r="B88" t="n">
-        <v>80150</v>
+        <v>57821</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>678337</v>
+        <v>678565</v>
       </c>
       <c r="R88" t="n">
-        <v>7105676</v>
+        <v>7105751</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9668,48 +9668,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126862249</v>
+        <v>126865255</v>
       </c>
       <c r="B89" t="n">
-        <v>57821</v>
+        <v>98365</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>223591</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9719,13 +9715,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>678565</v>
+        <v>678327</v>
       </c>
       <c r="R89" t="n">
-        <v>7105751</v>
+        <v>7105520</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9769,15 +9765,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10834,10 +10834,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126861188</v>
+        <v>126861120</v>
       </c>
       <c r="B100" t="n">
-        <v>78776</v>
+        <v>75137</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10845,21 +10845,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>310</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10869,10 +10869,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>678286</v>
+        <v>678361</v>
       </c>
       <c r="R100" t="n">
-        <v>7105527</v>
+        <v>7105711</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10935,48 +10935,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126868561</v>
+        <v>126866143</v>
       </c>
       <c r="B101" t="n">
-        <v>80150</v>
+        <v>79050</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>678322</v>
+        <v>678534</v>
       </c>
       <c r="R101" t="n">
-        <v>7105572</v>
+        <v>7105769</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11020,12 +11020,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11036,10 +11036,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126865242</v>
+        <v>126861054</v>
       </c>
       <c r="B102" t="n">
-        <v>79636</v>
+        <v>91330</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11047,34 +11047,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>678383</v>
+        <v>678337</v>
       </c>
       <c r="R102" t="n">
-        <v>7105681</v>
+        <v>7105668</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11121,12 +11121,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11137,7 +11137,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126861187</v>
+        <v>126861188</v>
       </c>
       <c r="B103" t="n">
         <v>78776</v>
@@ -11172,10 +11172,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>678280</v>
+        <v>678286</v>
       </c>
       <c r="R103" t="n">
-        <v>7105615</v>
+        <v>7105527</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11238,48 +11238,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126862245</v>
+        <v>126868561</v>
       </c>
       <c r="B104" t="n">
-        <v>57661</v>
+        <v>80150</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>678530</v>
+        <v>678322</v>
       </c>
       <c r="R104" t="n">
-        <v>7105781</v>
+        <v>7105572</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11323,22 +11323,26 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr"/>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126868554</v>
+        <v>126865242</v>
       </c>
       <c r="B105" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11346,46 +11350,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>678534</v>
+        <v>678383</v>
       </c>
       <c r="R105" t="n">
-        <v>7105773</v>
+        <v>7105681</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11432,12 +11424,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11448,10 +11440,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126861120</v>
+        <v>126861187</v>
       </c>
       <c r="B106" t="n">
-        <v>75137</v>
+        <v>78776</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11459,21 +11451,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>310</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11483,10 +11475,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>678361</v>
+        <v>678280</v>
       </c>
       <c r="R106" t="n">
-        <v>7105711</v>
+        <v>7105615</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11549,10 +11541,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126866143</v>
+        <v>126862245</v>
       </c>
       <c r="B107" t="n">
-        <v>79050</v>
+        <v>57661</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11560,21 +11552,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11584,13 +11576,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>678534</v>
+        <v>678530</v>
       </c>
       <c r="R107" t="n">
-        <v>7105769</v>
+        <v>7105781</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11634,26 +11626,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126861054</v>
+        <v>126868554</v>
       </c>
       <c r="B108" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11661,34 +11649,46 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>678337</v>
+        <v>678534</v>
       </c>
       <c r="R108" t="n">
-        <v>7105668</v>
+        <v>7105773</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11735,12 +11735,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -14343,32 +14343,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126861105</v>
+        <v>126861137</v>
       </c>
       <c r="B134" t="n">
-        <v>80025</v>
+        <v>78777</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14378,10 +14378,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>678330</v>
+        <v>678270</v>
       </c>
       <c r="R134" t="n">
-        <v>7105447</v>
+        <v>7105627</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14444,10 +14444,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126868588</v>
+        <v>126861138</v>
       </c>
       <c r="B135" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14455,21 +14455,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14479,10 +14479,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>678330</v>
+        <v>678295</v>
       </c>
       <c r="R135" t="n">
-        <v>7105451</v>
+        <v>7105595</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14529,12 +14529,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14545,10 +14545,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126868617</v>
+        <v>126861105</v>
       </c>
       <c r="B136" t="n">
-        <v>80056</v>
+        <v>80025</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14556,21 +14556,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14580,10 +14580,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>678328</v>
+        <v>678330</v>
       </c>
       <c r="R136" t="n">
-        <v>7105581</v>
+        <v>7105447</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14630,12 +14630,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14646,10 +14646,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126861307</v>
+        <v>126868588</v>
       </c>
       <c r="B137" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14657,21 +14657,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14681,10 +14681,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>678356</v>
+        <v>678330</v>
       </c>
       <c r="R137" t="n">
-        <v>7105708</v>
+        <v>7105451</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14731,12 +14731,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14747,32 +14747,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126861309</v>
+        <v>126868617</v>
       </c>
       <c r="B138" t="n">
-        <v>79018</v>
+        <v>80056</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14782,10 +14782,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>678368</v>
+        <v>678328</v>
       </c>
       <c r="R138" t="n">
-        <v>7105697</v>
+        <v>7105581</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14832,12 +14832,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14848,7 +14848,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126861262</v>
+        <v>126861307</v>
       </c>
       <c r="B139" t="n">
         <v>79018</v>
@@ -14883,10 +14883,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>678532</v>
+        <v>678356</v>
       </c>
       <c r="R139" t="n">
-        <v>7105725</v>
+        <v>7105708</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14949,7 +14949,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126861315</v>
+        <v>126861309</v>
       </c>
       <c r="B140" t="n">
         <v>79018</v>
@@ -14984,10 +14984,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>678354</v>
+        <v>678368</v>
       </c>
       <c r="R140" t="n">
-        <v>7105657</v>
+        <v>7105697</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15050,7 +15050,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126861322</v>
+        <v>126861262</v>
       </c>
       <c r="B141" t="n">
         <v>79018</v>
@@ -15085,10 +15085,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>678224</v>
+        <v>678532</v>
       </c>
       <c r="R141" t="n">
-        <v>7105630</v>
+        <v>7105725</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15151,7 +15151,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126862287</v>
+        <v>126861315</v>
       </c>
       <c r="B142" t="n">
         <v>79018</v>
@@ -15182,17 +15182,17 @@
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>678359</v>
+        <v>678354</v>
       </c>
       <c r="R142" t="n">
-        <v>7105587</v>
+        <v>7105657</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15236,22 +15236,26 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY142" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126861137</v>
+        <v>126861322</v>
       </c>
       <c r="B143" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15259,21 +15263,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15283,10 +15287,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>678270</v>
+        <v>678224</v>
       </c>
       <c r="R143" t="n">
-        <v>7105627</v>
+        <v>7105630</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15349,10 +15353,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126861138</v>
+        <v>126862287</v>
       </c>
       <c r="B144" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15360,37 +15364,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>678295</v>
+        <v>678359</v>
       </c>
       <c r="R144" t="n">
-        <v>7105595</v>
+        <v>7105587</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15434,19 +15438,15 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16388,10 +16388,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126865272</v>
+        <v>126865776</v>
       </c>
       <c r="B154" t="n">
-        <v>91330</v>
+        <v>79607</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16399,21 +16399,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16426,10 +16426,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>678324</v>
+        <v>678531</v>
       </c>
       <c r="R154" t="n">
-        <v>7105605</v>
+        <v>7105530</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16485,52 +16485,56 @@
           <t>Fredrik Wilde</t>
         </is>
       </c>
-      <c r="AY154" t="inlineStr"/>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126860442</v>
+        <v>126861112</v>
       </c>
       <c r="B155" t="n">
-        <v>79018</v>
+        <v>97325</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>678328</v>
+        <v>678264</v>
       </c>
       <c r="R155" t="n">
-        <v>7105453</v>
+        <v>7105660</v>
       </c>
       <c r="S155" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16557,19 +16561,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>09:34</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16584,12 +16578,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -16600,10 +16594,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126865310</v>
+        <v>126865272</v>
       </c>
       <c r="B156" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16611,34 +16605,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>678503</v>
+        <v>678324</v>
       </c>
       <c r="R156" t="n">
-        <v>7105771</v>
+        <v>7105605</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16679,67 +16676,64 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126861318</v>
+        <v>126865178</v>
       </c>
       <c r="B157" t="n">
-        <v>79018</v>
+        <v>80025</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>678328</v>
+        <v>678296</v>
       </c>
       <c r="R157" t="n">
-        <v>7105677</v>
+        <v>7105501</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16783,15 +16777,30 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -16802,45 +16811,48 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126865178</v>
+        <v>126865103</v>
       </c>
       <c r="B158" t="n">
-        <v>80025</v>
+        <v>80121</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>678296</v>
+        <v>678320</v>
       </c>
       <c r="R158" t="n">
-        <v>7105501</v>
+        <v>7105573</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16881,47 +16893,29 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126865103</v>
+        <v>126860442</v>
       </c>
       <c r="B159" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16929,40 +16923,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>678320</v>
+        <v>678328</v>
       </c>
       <c r="R159" t="n">
-        <v>7105573</v>
+        <v>7105453</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16989,40 +16980,53 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY159" t="inlineStr"/>
+          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126861057</v>
+        <v>126865310</v>
       </c>
       <c r="B160" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17030,48 +17034,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>678394</v>
+        <v>678503</v>
       </c>
       <c r="R160" t="n">
-        <v>7105671</v>
+        <v>7105771</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17118,12 +17108,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -17134,10 +17124,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126865776</v>
+        <v>126861318</v>
       </c>
       <c r="B161" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17145,37 +17135,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>678531</v>
+        <v>678328</v>
       </c>
       <c r="R161" t="n">
-        <v>7105530</v>
+        <v>7105677</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17216,19 +17203,18 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -17239,45 +17225,59 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126861112</v>
+        <v>126861057</v>
       </c>
       <c r="B162" t="n">
-        <v>97325</v>
+        <v>57661</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>678264</v>
+        <v>678394</v>
       </c>
       <c r="R162" t="n">
-        <v>7105660</v>
+        <v>7105671</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18472,51 +18472,48 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126865164</v>
+        <v>126862299</v>
       </c>
       <c r="B174" t="n">
-        <v>80121</v>
+        <v>98364</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>678313</v>
+        <v>678308</v>
       </c>
       <c r="R174" t="n">
-        <v>7105600</v>
+        <v>7105509</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18554,67 +18551,70 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126866157</v>
+        <v>126868598</v>
       </c>
       <c r="B175" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>678347</v>
+        <v>678394</v>
       </c>
       <c r="R175" t="n">
-        <v>7105620</v>
+        <v>7105689</v>
       </c>
       <c r="S175" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18644,6 +18644,11 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Delvis blommande, grovt uppskattat antal</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18658,12 +18663,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -18674,52 +18679,48 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126868598</v>
+        <v>126862264</v>
       </c>
       <c r="B176" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>678394</v>
+        <v>678322</v>
       </c>
       <c r="R176" t="n">
-        <v>7105689</v>
+        <v>7105485</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -18749,11 +18750,6 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Delvis blommande, grovt uppskattat antal</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18768,64 +18764,60 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY176" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126862299</v>
+        <v>126853218</v>
       </c>
       <c r="B177" t="n">
-        <v>98364</v>
+        <v>78777</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>678308</v>
+        <v>678500</v>
       </c>
       <c r="R177" t="n">
-        <v>7105509</v>
+        <v>7105568</v>
       </c>
       <c r="S177" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -18852,9 +18844,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18869,22 +18871,26 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY177" t="inlineStr"/>
+          <t>Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126862264</v>
+        <v>126865164</v>
       </c>
       <c r="B178" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18892,37 +18898,40 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>678322</v>
+        <v>678313</v>
       </c>
       <c r="R178" t="n">
-        <v>7105485</v>
+        <v>7105600</v>
       </c>
       <c r="S178" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -18960,28 +18969,29 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126853218</v>
+        <v>126866157</v>
       </c>
       <c r="B179" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18989,37 +18999,37 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>678500</v>
+        <v>678347</v>
       </c>
       <c r="R179" t="n">
-        <v>7105568</v>
+        <v>7105620</v>
       </c>
       <c r="S179" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19046,19 +19056,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>11:24</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19073,12 +19073,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -19311,10 +19311,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>126865243</v>
+        <v>126866142</v>
       </c>
       <c r="B182" t="n">
-        <v>57821</v>
+        <v>75142</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19322,21 +19322,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19346,13 +19346,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>678437</v>
+        <v>678327</v>
       </c>
       <c r="R182" t="n">
-        <v>7105642</v>
+        <v>7105562</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19396,12 +19396,12 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -19412,10 +19412,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>126866426</v>
+        <v>126865238</v>
       </c>
       <c r="B183" t="n">
-        <v>41365</v>
+        <v>75142</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19423,47 +19423,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>215713</v>
+        <v>6440</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>678428</v>
+        <v>678313</v>
       </c>
       <c r="R183" t="n">
-        <v>7105690</v>
+        <v>7105554</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19504,7 +19491,6 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -19516,7 +19502,7 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -19527,10 +19513,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>126866153</v>
+        <v>126865243</v>
       </c>
       <c r="B184" t="n">
-        <v>78777</v>
+        <v>57821</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19538,21 +19524,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19562,13 +19548,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>678378</v>
+        <v>678437</v>
       </c>
       <c r="R184" t="n">
-        <v>7105618</v>
+        <v>7105642</v>
       </c>
       <c r="S184" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19612,12 +19598,12 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
@@ -19628,10 +19614,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126866142</v>
+        <v>126866426</v>
       </c>
       <c r="B185" t="n">
-        <v>75142</v>
+        <v>41365</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19639,37 +19625,50 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6440</v>
+        <v>215713</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>678327</v>
+        <v>678428</v>
       </c>
       <c r="R185" t="n">
-        <v>7105562</v>
+        <v>7105690</v>
       </c>
       <c r="S185" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19707,18 +19706,19 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
@@ -19729,10 +19729,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>126865238</v>
+        <v>126866153</v>
       </c>
       <c r="B186" t="n">
-        <v>75142</v>
+        <v>78777</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19740,21 +19740,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19764,13 +19764,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>678313</v>
+        <v>678378</v>
       </c>
       <c r="R186" t="n">
-        <v>7105554</v>
+        <v>7105618</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19814,12 +19814,12 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
@@ -22409,32 +22409,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>126865855</v>
+        <v>126866024</v>
       </c>
       <c r="B212" t="n">
-        <v>91330</v>
+        <v>80149</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22447,10 +22447,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>678579</v>
+        <v>678594</v>
       </c>
       <c r="R212" t="n">
-        <v>7105578</v>
+        <v>7105682</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22514,32 +22514,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>126866024</v>
+        <v>126865855</v>
       </c>
       <c r="B213" t="n">
-        <v>80149</v>
+        <v>91330</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22552,10 +22552,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>678594</v>
+        <v>678579</v>
       </c>
       <c r="R213" t="n">
-        <v>7105682</v>
+        <v>7105578</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23888,10 +23888,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>126865442</v>
+        <v>126865445</v>
       </c>
       <c r="B226" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23899,21 +23899,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23923,10 +23923,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>678295</v>
+        <v>678319</v>
       </c>
       <c r="R226" t="n">
-        <v>7105600</v>
+        <v>7105572</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23989,10 +23989,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>126865445</v>
+        <v>126865442</v>
       </c>
       <c r="B227" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24000,21 +24000,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24024,10 +24024,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>678319</v>
+        <v>678295</v>
       </c>
       <c r="R227" t="n">
-        <v>7105572</v>
+        <v>7105600</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -2406,48 +2406,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126860448</v>
+        <v>126861083</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>678446</v>
+        <v>678271</v>
       </c>
       <c r="R19" t="n">
-        <v>7105699</v>
+        <v>7105610</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2474,19 +2474,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2501,12 +2491,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2517,45 +2507,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126865187</v>
+        <v>126861081</v>
       </c>
       <c r="B20" t="n">
-        <v>78424</v>
+        <v>80150</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>678622</v>
+        <v>678254</v>
       </c>
       <c r="R20" t="n">
-        <v>7105605</v>
+        <v>7105631</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2599,30 +2589,15 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2633,45 +2608,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126861142</v>
+        <v>126861202</v>
       </c>
       <c r="B21" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>678244</v>
+        <v>678291</v>
       </c>
       <c r="R21" t="n">
-        <v>7105642</v>
+        <v>7105551</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,11 +2688,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2739,7 +2718,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126861312</v>
+        <v>126860448</v>
       </c>
       <c r="B22" t="n">
         <v>79018</v>
@@ -2770,17 +2749,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>678383</v>
+        <v>678446</v>
       </c>
       <c r="R22" t="n">
-        <v>7105668</v>
+        <v>7105699</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2807,9 +2786,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2824,12 +2813,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2840,10 +2829,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126861260</v>
+        <v>126865187</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>78424</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,34 +2840,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>678449</v>
+        <v>678622</v>
       </c>
       <c r="R23" t="n">
-        <v>7105699</v>
+        <v>7105605</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,15 +2911,30 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2941,54 +2945,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126861202</v>
+        <v>126861142</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>80121</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>678291</v>
+        <v>678244</v>
       </c>
       <c r="R24" t="n">
-        <v>7105551</v>
+        <v>7105642</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,6 +3016,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3051,32 +3051,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126861083</v>
+        <v>126861312</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>678271</v>
+        <v>678383</v>
       </c>
       <c r="R25" t="n">
-        <v>7105610</v>
+        <v>7105668</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,32 +3152,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126861081</v>
+        <v>126861260</v>
       </c>
       <c r="B26" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>678254</v>
+        <v>678449</v>
       </c>
       <c r="R26" t="n">
-        <v>7105631</v>
+        <v>7105699</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -7211,48 +7211,62 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126868541</v>
+        <v>126853937</v>
       </c>
       <c r="B65" t="n">
-        <v>75142</v>
+        <v>98448</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>678322</v>
+        <v>678352</v>
       </c>
       <c r="R65" t="n">
-        <v>7105557</v>
+        <v>7105670</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7279,9 +7293,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7296,26 +7320,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126861165</v>
+        <v>126868541</v>
       </c>
       <c r="B66" t="n">
-        <v>80121</v>
+        <v>75142</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7323,21 +7343,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7347,10 +7367,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>678337</v>
+        <v>678322</v>
       </c>
       <c r="R66" t="n">
-        <v>7105669</v>
+        <v>7105557</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7397,12 +7417,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7413,32 +7433,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126861100</v>
+        <v>126861165</v>
       </c>
       <c r="B67" t="n">
-        <v>80025</v>
+        <v>80121</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7448,10 +7468,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>678335</v>
+        <v>678337</v>
       </c>
       <c r="R67" t="n">
-        <v>7105661</v>
+        <v>7105669</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7514,48 +7534,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126856160</v>
+        <v>126861100</v>
       </c>
       <c r="B68" t="n">
-        <v>78424</v>
+        <v>80025</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6437</v>
+        <v>6456</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>678553</v>
+        <v>678335</v>
       </c>
       <c r="R68" t="n">
-        <v>7105588</v>
+        <v>7105661</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7582,19 +7602,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:32</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7609,12 +7619,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7625,10 +7635,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126860445</v>
+        <v>126856160</v>
       </c>
       <c r="B69" t="n">
-        <v>80121</v>
+        <v>78424</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7636,37 +7646,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>678290</v>
+        <v>678553</v>
       </c>
       <c r="R69" t="n">
-        <v>7105581</v>
+        <v>7105588</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7695,7 +7705,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7705,7 +7715,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7720,12 +7730,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7736,49 +7746,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126868599</v>
+        <v>126860445</v>
       </c>
       <c r="B70" t="n">
-        <v>98448</v>
+        <v>80121</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
         <v>678290</v>
       </c>
       <c r="R70" t="n">
-        <v>7105494</v>
+        <v>7105581</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7808,14 +7814,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Delvis blommande, grovt uppskattat antal</t>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7830,12 +7841,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7846,45 +7857,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126861113</v>
+        <v>126865314</v>
       </c>
       <c r="B71" t="n">
-        <v>97325</v>
+        <v>79018</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>678242</v>
+        <v>678506</v>
       </c>
       <c r="R71" t="n">
-        <v>7105626</v>
+        <v>7105716</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7931,12 +7942,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7947,62 +7958,59 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126853937</v>
+        <v>126864836</v>
       </c>
       <c r="B72" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>678352</v>
+        <v>678301</v>
       </c>
       <c r="R72" t="n">
-        <v>7105670</v>
+        <v>7105516</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8029,46 +8037,37 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126865314</v>
+        <v>126862290</v>
       </c>
       <c r="B73" t="n">
         <v>79018</v>
@@ -8103,13 +8102,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>678506</v>
+        <v>678323</v>
       </c>
       <c r="R73" t="n">
-        <v>7105716</v>
+        <v>7105490</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8153,72 +8152,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126864836</v>
+        <v>126861053</v>
       </c>
       <c r="B74" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>678301</v>
+        <v>678315</v>
       </c>
       <c r="R74" t="n">
-        <v>7105516</v>
+        <v>7105477</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8259,26 +8243,29 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126862290</v>
+        <v>126862289</v>
       </c>
       <c r="B75" t="n">
         <v>79018</v>
@@ -8313,10 +8300,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>678323</v>
+        <v>678303</v>
       </c>
       <c r="R75" t="n">
-        <v>7105490</v>
+        <v>7105511</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8375,45 +8362,49 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126861053</v>
+        <v>126868599</v>
       </c>
       <c r="B76" t="n">
-        <v>91295</v>
+        <v>98448</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>678315</v>
+        <v>678290</v>
       </c>
       <c r="R76" t="n">
-        <v>7105477</v>
+        <v>7105494</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8448,6 +8439,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Delvis blommande, grovt uppskattat antal</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8460,12 +8456,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8476,48 +8472,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126862289</v>
+        <v>126861113</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>97325</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>678303</v>
+        <v>678242</v>
       </c>
       <c r="R77" t="n">
-        <v>7105511</v>
+        <v>7105626</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8561,15 +8557,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10834,10 +10834,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126861054</v>
+        <v>126865242</v>
       </c>
       <c r="B100" t="n">
-        <v>91330</v>
+        <v>79636</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10845,34 +10845,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>678337</v>
+        <v>678383</v>
       </c>
       <c r="R100" t="n">
-        <v>7105668</v>
+        <v>7105681</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10919,12 +10919,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10935,10 +10935,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126861120</v>
+        <v>126866158</v>
       </c>
       <c r="B101" t="n">
-        <v>75137</v>
+        <v>79018</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10946,37 +10946,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>678361</v>
+        <v>678283</v>
       </c>
       <c r="R101" t="n">
-        <v>7105711</v>
+        <v>7105510</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11020,12 +11020,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11036,10 +11036,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126866143</v>
+        <v>126861321</v>
       </c>
       <c r="B102" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11047,37 +11047,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>678534</v>
+        <v>678283</v>
       </c>
       <c r="R102" t="n">
-        <v>7105769</v>
+        <v>7105646</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11121,12 +11121,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11137,32 +11137,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126868561</v>
+        <v>126861325</v>
       </c>
       <c r="B103" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11172,10 +11172,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>678322</v>
+        <v>678282</v>
       </c>
       <c r="R103" t="n">
-        <v>7105572</v>
+        <v>7105617</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11222,12 +11222,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård, Peder Winding</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11238,10 +11238,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126866158</v>
+        <v>126861054</v>
       </c>
       <c r="B104" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11249,37 +11249,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>678283</v>
+        <v>678337</v>
       </c>
       <c r="R104" t="n">
-        <v>7105510</v>
+        <v>7105668</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11323,12 +11323,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11339,10 +11339,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126861321</v>
+        <v>126861120</v>
       </c>
       <c r="B105" t="n">
-        <v>79018</v>
+        <v>75137</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11350,21 +11350,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11374,10 +11374,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>678283</v>
+        <v>678361</v>
       </c>
       <c r="R105" t="n">
-        <v>7105646</v>
+        <v>7105711</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11440,10 +11440,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126861325</v>
+        <v>126866143</v>
       </c>
       <c r="B106" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11451,37 +11451,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>678282</v>
+        <v>678534</v>
       </c>
       <c r="R106" t="n">
-        <v>7105617</v>
+        <v>7105769</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11525,12 +11525,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård, Peder Winding</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11541,10 +11541,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126864769</v>
+        <v>126861188</v>
       </c>
       <c r="B107" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11552,37 +11552,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>678334</v>
+        <v>678286</v>
       </c>
       <c r="R107" t="n">
-        <v>7105667</v>
+        <v>7105527</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11623,19 +11620,18 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Malin Löfgren, Mattias Dalkvist, Anne Siivola, Philipp Weiss, Carl Jansson, Peder Winding, Martin Axegård, Fredrik Wilde, Vilhelm Kroon, Cajsa Björkén, Hedda Bring</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11646,32 +11642,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126861188</v>
+        <v>126868561</v>
       </c>
       <c r="B108" t="n">
-        <v>78776</v>
+        <v>80150</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11681,10 +11677,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>678286</v>
+        <v>678322</v>
       </c>
       <c r="R108" t="n">
-        <v>7105527</v>
+        <v>7105572</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11731,12 +11727,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11747,10 +11743,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126865242</v>
+        <v>126864769</v>
       </c>
       <c r="B109" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11758,34 +11754,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>678383</v>
+        <v>678334</v>
       </c>
       <c r="R109" t="n">
-        <v>7105681</v>
+        <v>7105667</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11826,18 +11825,19 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Lotta Ihse, Malin Löfgren, Mattias Dalkvist, Anne Siivola, Philipp Weiss, Carl Jansson, Peder Winding, Martin Axegård, Fredrik Wilde, Vilhelm Kroon, Cajsa Björkén, Hedda Bring</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12361,10 +12361,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126862297</v>
+        <v>126865226</v>
       </c>
       <c r="B115" t="n">
-        <v>98365</v>
+        <v>80150</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12372,37 +12372,40 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>678417</v>
+        <v>678313</v>
       </c>
       <c r="R115" t="n">
-        <v>7105592</v>
+        <v>7105600</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12440,28 +12443,29 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126853157</v>
+        <v>126868550</v>
       </c>
       <c r="B116" t="n">
-        <v>57821</v>
+        <v>79636</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12469,38 +12473,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>678507</v>
+        <v>678293</v>
       </c>
       <c r="R116" t="n">
-        <v>7105595</v>
+        <v>7105493</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12530,19 +12530,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12557,44 +12547,48 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126862274</v>
+        <v>126862267</v>
       </c>
       <c r="B117" t="n">
-        <v>58338</v>
+        <v>80121</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103044</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12604,10 +12598,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>678512</v>
+        <v>678314</v>
       </c>
       <c r="R117" t="n">
-        <v>7105616</v>
+        <v>7105563</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12666,48 +12660,48 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126852438</v>
+        <v>126862274</v>
       </c>
       <c r="B118" t="n">
-        <v>78777</v>
+        <v>58338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>103044</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>678438</v>
+        <v>678512</v>
       </c>
       <c r="R118" t="n">
-        <v>7105684</v>
+        <v>7105616</v>
       </c>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12734,19 +12728,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12761,26 +12745,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126865316</v>
+        <v>126852438</v>
       </c>
       <c r="B119" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12788,37 +12768,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>678353</v>
+        <v>678438</v>
       </c>
       <c r="R119" t="n">
-        <v>7105503</v>
+        <v>7105684</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12845,9 +12825,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12862,12 +12852,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12878,7 +12868,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126865185</v>
+        <v>126865316</v>
       </c>
       <c r="B120" t="n">
         <v>79018</v>
@@ -12909,14 +12899,14 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>678603</v>
+        <v>678353</v>
       </c>
       <c r="R120" t="n">
-        <v>7105573</v>
+        <v>7105503</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12960,30 +12950,15 @@
       <c r="AG120" t="b">
         <v>0</v>
       </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -12994,10 +12969,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126868550</v>
+        <v>126865185</v>
       </c>
       <c r="B121" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13005,34 +12980,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>678293</v>
+        <v>678603</v>
       </c>
       <c r="R121" t="n">
-        <v>7105493</v>
+        <v>7105573</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13076,15 +13051,30 @@
       <c r="AG121" t="b">
         <v>0</v>
       </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13095,10 +13085,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126862267</v>
+        <v>126853157</v>
       </c>
       <c r="B122" t="n">
-        <v>80121</v>
+        <v>57821</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13106,37 +13096,41 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>678314</v>
+        <v>678507</v>
       </c>
       <c r="R122" t="n">
-        <v>7105563</v>
+        <v>7105595</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13163,9 +13157,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13180,22 +13184,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126865226</v>
+        <v>126862297</v>
       </c>
       <c r="B123" t="n">
-        <v>80150</v>
+        <v>98365</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13203,40 +13207,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>678313</v>
+        <v>678417</v>
       </c>
       <c r="R123" t="n">
-        <v>7105600</v>
+        <v>7105592</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13274,19 +13275,18 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -14343,32 +14343,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126861309</v>
+        <v>126861105</v>
       </c>
       <c r="B134" t="n">
-        <v>79018</v>
+        <v>80025</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14378,10 +14378,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>678368</v>
+        <v>678330</v>
       </c>
       <c r="R134" t="n">
-        <v>7105697</v>
+        <v>7105447</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14444,10 +14444,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126861262</v>
+        <v>126868588</v>
       </c>
       <c r="B135" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14455,21 +14455,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14479,10 +14479,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>678532</v>
+        <v>678330</v>
       </c>
       <c r="R135" t="n">
-        <v>7105725</v>
+        <v>7105451</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14529,12 +14529,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14545,7 +14545,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126861315</v>
+        <v>126861262</v>
       </c>
       <c r="B136" t="n">
         <v>79018</v>
@@ -14580,10 +14580,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>678354</v>
+        <v>678532</v>
       </c>
       <c r="R136" t="n">
-        <v>7105657</v>
+        <v>7105725</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14646,7 +14646,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126861322</v>
+        <v>126861315</v>
       </c>
       <c r="B137" t="n">
         <v>79018</v>
@@ -14681,10 +14681,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>678224</v>
+        <v>678354</v>
       </c>
       <c r="R137" t="n">
-        <v>7105630</v>
+        <v>7105657</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14747,7 +14747,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126862287</v>
+        <v>126861322</v>
       </c>
       <c r="B138" t="n">
         <v>79018</v>
@@ -14778,17 +14778,17 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>678359</v>
+        <v>678224</v>
       </c>
       <c r="R138" t="n">
-        <v>7105587</v>
+        <v>7105630</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14832,19 +14832,23 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126861307</v>
+        <v>126862287</v>
       </c>
       <c r="B139" t="n">
         <v>79018</v>
@@ -14875,17 +14879,17 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>678356</v>
+        <v>678359</v>
       </c>
       <c r="R139" t="n">
-        <v>7105708</v>
+        <v>7105587</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14929,48 +14933,44 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126861105</v>
+        <v>126861137</v>
       </c>
       <c r="B140" t="n">
-        <v>80025</v>
+        <v>78777</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14980,10 +14980,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>678330</v>
+        <v>678270</v>
       </c>
       <c r="R140" t="n">
-        <v>7105447</v>
+        <v>7105627</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15046,10 +15046,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126868588</v>
+        <v>126861138</v>
       </c>
       <c r="B141" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15057,21 +15057,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15081,10 +15081,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>678330</v>
+        <v>678295</v>
       </c>
       <c r="R141" t="n">
-        <v>7105451</v>
+        <v>7105595</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15131,12 +15131,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15147,32 +15147,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126868617</v>
+        <v>126861307</v>
       </c>
       <c r="B142" t="n">
-        <v>80056</v>
+        <v>79018</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15182,10 +15182,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>678328</v>
+        <v>678356</v>
       </c>
       <c r="R142" t="n">
-        <v>7105581</v>
+        <v>7105708</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15232,12 +15232,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Philipp Weiss, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Malin Löfgren</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15248,32 +15248,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126861137</v>
+        <v>126868617</v>
       </c>
       <c r="B143" t="n">
-        <v>78777</v>
+        <v>80056</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>6457</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15283,10 +15283,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>678270</v>
+        <v>678328</v>
       </c>
       <c r="R143" t="n">
-        <v>7105627</v>
+        <v>7105581</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15333,12 +15333,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Philipp Weiss, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -15349,10 +15349,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126861138</v>
+        <v>126861309</v>
       </c>
       <c r="B144" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15360,21 +15360,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15384,10 +15384,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>678295</v>
+        <v>678368</v>
       </c>
       <c r="R144" t="n">
-        <v>7105595</v>
+        <v>7105697</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15450,58 +15450,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126865296</v>
+        <v>126868627</v>
       </c>
       <c r="B145" t="n">
-        <v>41365</v>
+        <v>79994</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>215713</v>
+        <v>392</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>678332</v>
+        <v>678330</v>
       </c>
       <c r="R145" t="n">
-        <v>7105461</v>
+        <v>7105453</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15548,12 +15535,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Philipp Weiss, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15564,32 +15551,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126868627</v>
+        <v>126868607</v>
       </c>
       <c r="B146" t="n">
-        <v>79994</v>
+        <v>91348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>392</v>
+        <v>5432</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15599,10 +15586,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>678330</v>
+        <v>678439</v>
       </c>
       <c r="R146" t="n">
-        <v>7105453</v>
+        <v>7105681</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15665,10 +15652,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126868607</v>
+        <v>126868596</v>
       </c>
       <c r="B147" t="n">
-        <v>91348</v>
+        <v>78776</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15676,21 +15663,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15700,10 +15687,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>678439</v>
+        <v>678293</v>
       </c>
       <c r="R147" t="n">
-        <v>7105681</v>
+        <v>7105493</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15755,7 +15742,7 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Philipp Weiss, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Malin Löfgren</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15766,10 +15753,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126868596</v>
+        <v>126851438</v>
       </c>
       <c r="B148" t="n">
-        <v>78776</v>
+        <v>80121</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15777,37 +15764,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>678293</v>
+        <v>678352</v>
       </c>
       <c r="R148" t="n">
-        <v>7105493</v>
+        <v>7105670</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15834,9 +15821,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15851,26 +15848,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126851438</v>
+        <v>126861324</v>
       </c>
       <c r="B149" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15878,37 +15871,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>678352</v>
+        <v>678264</v>
       </c>
       <c r="R149" t="n">
-        <v>7105670</v>
+        <v>7105625</v>
       </c>
       <c r="S149" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15935,19 +15928,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>10:23</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15962,22 +15945,26 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126861324</v>
+        <v>126865296</v>
       </c>
       <c r="B150" t="n">
-        <v>79018</v>
+        <v>41365</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15985,34 +15972,47 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>215713</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>678264</v>
+        <v>678332</v>
       </c>
       <c r="R150" t="n">
-        <v>7105625</v>
+        <v>7105461</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16059,12 +16059,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -16388,10 +16388,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126860442</v>
+        <v>126865272</v>
       </c>
       <c r="B154" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16399,37 +16399,40 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>678328</v>
+        <v>678324</v>
       </c>
       <c r="R154" t="n">
-        <v>7105453</v>
+        <v>7105605</v>
       </c>
       <c r="S154" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16456,88 +16459,75 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY154" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126865310</v>
+        <v>126865178</v>
       </c>
       <c r="B155" t="n">
-        <v>79018</v>
+        <v>80025</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnberget, Käringberget EP, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>678503</v>
+        <v>678296</v>
       </c>
       <c r="R155" t="n">
-        <v>7105771</v>
+        <v>7105501</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16581,15 +16571,30 @@
       <c r="AG155" t="b">
         <v>0</v>
       </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -16600,10 +16605,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126861318</v>
+        <v>126865103</v>
       </c>
       <c r="B156" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16611,34 +16616,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>678328</v>
+        <v>678320</v>
       </c>
       <c r="R156" t="n">
-        <v>7105677</v>
+        <v>7105573</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16679,32 +16687,29 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126865272</v>
+        <v>126860442</v>
       </c>
       <c r="B157" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16712,40 +16717,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>678324</v>
+        <v>678328</v>
       </c>
       <c r="R157" t="n">
-        <v>7105605</v>
+        <v>7105453</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16772,75 +16774,88 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY157" t="inlineStr"/>
+          <t>Mattias Dalkvist, Philipp Weiss, Cajsa Björkén, Carl Jansson, Fredrik Wilde, Anne Siivola, Vilhelm Kroon, Lotta Ihse, Hedda Bring, Malin Löfgren, Peder Winding, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126865178</v>
+        <v>126865310</v>
       </c>
       <c r="B158" t="n">
-        <v>80025</v>
+        <v>79018</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Käringberget EP, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>678296</v>
+        <v>678503</v>
       </c>
       <c r="R158" t="n">
-        <v>7105501</v>
+        <v>7105771</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16884,30 +16899,15 @@
       <c r="AG158" t="b">
         <v>0</v>
       </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Carl Jansson, Philipp Weiss, Cajsa Björkén, Fredrik Wilde, Peder Winding, Hedda Bring, Mattias Dalkvist, Martin Axegård, Vilhelm Kroon</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -16918,10 +16918,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126865103</v>
+        <v>126861318</v>
       </c>
       <c r="B159" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16929,37 +16929,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>678320</v>
+        <v>678328</v>
       </c>
       <c r="R159" t="n">
-        <v>7105573</v>
+        <v>7105677</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17000,22 +16997,25 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY159" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17134,45 +17134,48 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126861112</v>
+        <v>126865776</v>
       </c>
       <c r="B161" t="n">
-        <v>97325</v>
+        <v>79607</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>678264</v>
+        <v>678531</v>
       </c>
       <c r="R161" t="n">
-        <v>7105660</v>
+        <v>7105530</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17213,18 +17216,19 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -17235,48 +17239,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126865776</v>
+        <v>126861112</v>
       </c>
       <c r="B162" t="n">
-        <v>79607</v>
+        <v>97325</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>678531</v>
+        <v>678264</v>
       </c>
       <c r="R162" t="n">
-        <v>7105530</v>
+        <v>7105660</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17317,19 +17318,18 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -17538,7 +17538,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126862283</v>
+        <v>126861308</v>
       </c>
       <c r="B165" t="n">
         <v>79018</v>
@@ -17569,17 +17569,17 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>678643</v>
+        <v>678365</v>
       </c>
       <c r="R165" t="n">
-        <v>7105684</v>
+        <v>7105710</v>
       </c>
       <c r="S165" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17623,19 +17623,23 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY165" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126862282</v>
+        <v>126861264</v>
       </c>
       <c r="B166" t="n">
         <v>79018</v>
@@ -17666,17 +17670,17 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>678519</v>
+        <v>678524</v>
       </c>
       <c r="R166" t="n">
-        <v>7105769</v>
+        <v>7105764</v>
       </c>
       <c r="S166" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17720,15 +17724,19 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY166" t="inlineStr"/>
+          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17843,48 +17851,52 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126861308</v>
+        <v>126851795</v>
       </c>
       <c r="B168" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>678365</v>
+        <v>678356</v>
       </c>
       <c r="R168" t="n">
-        <v>7105710</v>
+        <v>7105581</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17911,9 +17923,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17928,12 +17950,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -17944,45 +17966,54 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126861323</v>
+        <v>126861196</v>
       </c>
       <c r="B169" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>678250</v>
+        <v>678405</v>
       </c>
       <c r="R169" t="n">
-        <v>7105611</v>
+        <v>7105696</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18045,7 +18076,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126861264</v>
+        <v>126861323</v>
       </c>
       <c r="B170" t="n">
         <v>79018</v>
@@ -18080,10 +18111,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>678524</v>
+        <v>678250</v>
       </c>
       <c r="R170" t="n">
-        <v>7105764</v>
+        <v>7105611</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18135,7 +18166,7 @@
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -18247,52 +18278,48 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126851795</v>
+        <v>126862283</v>
       </c>
       <c r="B172" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>678356</v>
+        <v>678643</v>
       </c>
       <c r="R172" t="n">
-        <v>7105581</v>
+        <v>7105684</v>
       </c>
       <c r="S172" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18319,19 +18346,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18346,73 +18363,60 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY172" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126861196</v>
+        <v>126862282</v>
       </c>
       <c r="B173" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>678405</v>
+        <v>678519</v>
       </c>
       <c r="R173" t="n">
-        <v>7105696</v>
+        <v>7105769</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18456,26 +18460,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY173" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126862264</v>
+        <v>126865164</v>
       </c>
       <c r="B174" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18483,37 +18483,40 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>678322</v>
+        <v>678313</v>
       </c>
       <c r="R174" t="n">
-        <v>7105485</v>
+        <v>7105600</v>
       </c>
       <c r="S174" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18551,28 +18554,29 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126853218</v>
+        <v>126866157</v>
       </c>
       <c r="B175" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18580,37 +18584,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>678500</v>
+        <v>678347</v>
       </c>
       <c r="R175" t="n">
-        <v>7105568</v>
+        <v>7105620</v>
       </c>
       <c r="S175" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18637,19 +18641,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>11:24</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18664,12 +18658,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -18680,51 +18674,48 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126865164</v>
+        <v>126862299</v>
       </c>
       <c r="B176" t="n">
-        <v>80121</v>
+        <v>98365</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>678313</v>
+        <v>678308</v>
       </c>
       <c r="R176" t="n">
-        <v>7105600</v>
+        <v>7105509</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -18762,67 +18753,70 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126866157</v>
+        <v>126868598</v>
       </c>
       <c r="B177" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>678347</v>
+        <v>678394</v>
       </c>
       <c r="R177" t="n">
-        <v>7105620</v>
+        <v>7105689</v>
       </c>
       <c r="S177" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -18852,6 +18846,11 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Delvis blommande, grovt uppskattat antal</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18866,12 +18865,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -18882,10 +18881,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126862299</v>
+        <v>126861090</v>
       </c>
       <c r="B178" t="n">
-        <v>98365</v>
+        <v>98469</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18893,37 +18892,42 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>678308</v>
+        <v>678253</v>
       </c>
       <c r="R178" t="n">
-        <v>7105509</v>
+        <v>7105629</v>
       </c>
       <c r="S178" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -18967,64 +18971,64 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY178" t="inlineStr"/>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126868598</v>
+        <v>126862264</v>
       </c>
       <c r="B179" t="n">
-        <v>98448</v>
+        <v>78777</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>678394</v>
+        <v>678322</v>
       </c>
       <c r="R179" t="n">
-        <v>7105689</v>
+        <v>7105485</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19054,11 +19058,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Delvis blommande, grovt uppskattat antal</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19073,69 +19072,60 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY179" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126861090</v>
+        <v>126853218</v>
       </c>
       <c r="B180" t="n">
-        <v>98469</v>
+        <v>78777</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Svarttjärnen, Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>678253</v>
+        <v>678500</v>
       </c>
       <c r="R180" t="n">
-        <v>7105629</v>
+        <v>7105568</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19162,9 +19152,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19179,12 +19179,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
@@ -20870,45 +20870,49 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126863395</v>
+        <v>126868601</v>
       </c>
       <c r="B197" t="n">
-        <v>98448</v>
+        <v>92095</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>678285</v>
+        <v>678322</v>
       </c>
       <c r="R197" t="n">
-        <v>7105493</v>
+        <v>7105572</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20943,6 +20947,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>På klen asplåga</t>
+        </is>
+      </c>
       <c r="AD197" t="b">
         <v>0</v>
       </c>
@@ -20955,12 +20964,12 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Philipp Weiss, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -20971,10 +20980,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>126861139</v>
+        <v>126865772</v>
       </c>
       <c r="B198" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20982,34 +20991,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>678244</v>
+        <v>678531</v>
       </c>
       <c r="R198" t="n">
-        <v>7105643</v>
+        <v>7105530</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21050,18 +21062,19 @@
       <c r="AE198" t="b">
         <v>0</v>
       </c>
+      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -21072,10 +21085,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126866155</v>
+        <v>126868551</v>
       </c>
       <c r="B199" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21083,37 +21096,37 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>678318</v>
+        <v>678369</v>
       </c>
       <c r="R199" t="n">
-        <v>7105498</v>
+        <v>7105652</v>
       </c>
       <c r="S199" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21157,12 +21170,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -21173,10 +21186,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126868601</v>
+        <v>126868587</v>
       </c>
       <c r="B200" t="n">
-        <v>92095</v>
+        <v>80121</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21184,38 +21197,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>366</v>
+        <v>6458</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>678322</v>
+        <v>678316</v>
       </c>
       <c r="R200" t="n">
-        <v>7105572</v>
+        <v>7105562</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21250,11 +21259,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>På klen asplåga</t>
-        </is>
-      </c>
       <c r="AD200" t="b">
         <v>0</v>
       </c>
@@ -21272,7 +21276,7 @@
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Philipp Weiss, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Malin Löfgren</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -21283,48 +21287,45 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>126865772</v>
+        <v>126868616</v>
       </c>
       <c r="B201" t="n">
-        <v>78685</v>
+        <v>80056</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>353</v>
+        <v>6457</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>678531</v>
+        <v>678314</v>
       </c>
       <c r="R201" t="n">
-        <v>7105530</v>
+        <v>7105567</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21365,19 +21366,18 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
-      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Philipp Weiss, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -21388,10 +21388,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>126868551</v>
+        <v>126868597</v>
       </c>
       <c r="B202" t="n">
-        <v>79636</v>
+        <v>78776</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21399,21 +21399,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21489,45 +21489,49 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>126868587</v>
+        <v>126868614</v>
       </c>
       <c r="B203" t="n">
-        <v>80121</v>
+        <v>98365</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>678316</v>
+        <v>678329</v>
       </c>
       <c r="R203" t="n">
-        <v>7105562</v>
+        <v>7105527</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21579,7 +21583,7 @@
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Philipp Weiss, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
@@ -21590,45 +21594,54 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>126868616</v>
+        <v>126861201</v>
       </c>
       <c r="B204" t="n">
-        <v>80056</v>
+        <v>98448</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>678314</v>
+        <v>678275</v>
       </c>
       <c r="R204" t="n">
-        <v>7105567</v>
+        <v>7105633</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21675,12 +21688,12 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Philipp Weiss, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Malin Löfgren</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
@@ -21691,45 +21704,45 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>126868597</v>
+        <v>126863395</v>
       </c>
       <c r="B205" t="n">
-        <v>78776</v>
+        <v>98448</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>678369</v>
+        <v>678285</v>
       </c>
       <c r="R205" t="n">
-        <v>7105652</v>
+        <v>7105493</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21776,12 +21789,12 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
@@ -21792,49 +21805,45 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>126868614</v>
+        <v>126861139</v>
       </c>
       <c r="B206" t="n">
-        <v>98365</v>
+        <v>78777</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>678329</v>
+        <v>678244</v>
       </c>
       <c r="R206" t="n">
-        <v>7105527</v>
+        <v>7105643</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21881,12 +21890,12 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Philipp Weiss, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Malin Löfgren</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
@@ -21897,57 +21906,48 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>126861201</v>
+        <v>126866155</v>
       </c>
       <c r="B207" t="n">
-        <v>98448</v>
+        <v>78777</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>678275</v>
+        <v>678318</v>
       </c>
       <c r="R207" t="n">
-        <v>7105633</v>
+        <v>7105498</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -21991,12 +21991,12 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
@@ -23479,32 +23479,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>126865446</v>
+        <v>126865454</v>
       </c>
       <c r="B222" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23514,10 +23514,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>678289</v>
+        <v>678384</v>
       </c>
       <c r="R222" t="n">
-        <v>7105512</v>
+        <v>7105660</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23550,11 +23550,6 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>1 ex</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23585,32 +23580,32 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>126865454</v>
+        <v>126865446</v>
       </c>
       <c r="B223" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23620,10 +23615,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>678384</v>
+        <v>678289</v>
       </c>
       <c r="R223" t="n">
-        <v>7105660</v>
+        <v>7105512</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23656,6 +23651,11 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23888,10 +23888,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>126865442</v>
+        <v>126865445</v>
       </c>
       <c r="B226" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23899,21 +23899,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23923,10 +23923,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>678295</v>
+        <v>678319</v>
       </c>
       <c r="R226" t="n">
-        <v>7105600</v>
+        <v>7105572</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23989,10 +23989,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>126865445</v>
+        <v>126865442</v>
       </c>
       <c r="B227" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24000,21 +24000,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24024,10 +24024,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>678319</v>
+        <v>678295</v>
       </c>
       <c r="R227" t="n">
-        <v>7105572</v>
+        <v>7105600</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY230"/>
+  <dimension ref="A1:AY232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22412,7 +22412,7 @@
         <v>126865855</v>
       </c>
       <c r="B212" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>126866024</v>
       </c>
       <c r="B213" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>126865940</v>
       </c>
       <c r="B214" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>126865791</v>
       </c>
       <c r="B215" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>126865945</v>
       </c>
       <c r="B216" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>126865787</v>
       </c>
       <c r="B217" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>126865996</v>
       </c>
       <c r="B218" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>126866090</v>
       </c>
       <c r="B219" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>126865890</v>
       </c>
       <c r="B220" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
         <v>126865437</v>
       </c>
       <c r="B221" t="n">
-        <v>79042</v>
+        <v>79044</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>126865454</v>
       </c>
       <c r="B222" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>126865446</v>
       </c>
       <c r="B223" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>126865428</v>
       </c>
       <c r="B224" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>126865452</v>
       </c>
       <c r="B225" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>126865445</v>
       </c>
       <c r="B226" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>126865442</v>
       </c>
       <c r="B227" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24090,32 +24090,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>126865431</v>
+        <v>126865443</v>
       </c>
       <c r="B228" t="n">
-        <v>80046</v>
+        <v>78779</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6003719</v>
+        <v>228912</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -24125,10 +24125,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>678319</v>
+        <v>678252</v>
       </c>
       <c r="R228" t="n">
-        <v>7105574</v>
+        <v>7105495</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24191,32 +24191,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>126865443</v>
+        <v>126865431</v>
       </c>
       <c r="B229" t="n">
-        <v>78777</v>
+        <v>80048</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>228912</v>
+        <v>6003719</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Traslav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scytinium lichenoides</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24226,10 +24226,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>678252</v>
+        <v>678319</v>
       </c>
       <c r="R229" t="n">
-        <v>7105495</v>
+        <v>7105574</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24295,7 +24295,7 @@
         <v>126865453</v>
       </c>
       <c r="B230" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24395,6 +24395,218 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>127735630</v>
+      </c>
+      <c r="B231" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Fredrika, Ång</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>678435</v>
+      </c>
+      <c r="R231" t="n">
+        <v>7105491</v>
+      </c>
+      <c r="S231" t="n">
+        <v>10</v>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT231" t="inlineStr"/>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>127735621</v>
+      </c>
+      <c r="B232" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Fredrika, Ång</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>678330</v>
+      </c>
+      <c r="R232" t="n">
+        <v>7105671</v>
+      </c>
+      <c r="S232" t="n">
+        <v>10</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT232" t="inlineStr"/>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -23468,7 +23468,7 @@
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Carl Jansson, Cajsa Björkén, Fredrik Wilde, Malin Löfgren, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Malin Löfgren, Fredrik Wilde, Cajsa Björkén, Carl Jansson</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
@@ -23675,7 +23675,7 @@
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Carl Jansson, Cajsa Björkén, Fredrik Wilde, Malin Löfgren, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Malin Löfgren, Fredrik Wilde, Cajsa Björkén, Carl Jansson</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Carl Jansson, Cajsa Björkén, Fredrik Wilde, Malin Löfgren, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Carl Jansson, Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Malin Löfgren, Fredrik Wilde, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -23978,7 +23978,7 @@
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Carl Jansson, Cajsa Björkén, Fredrik Wilde, Malin Löfgren, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Malin Löfgren, Fredrik Wilde, Cajsa Björkén, Carl Jansson</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
@@ -24079,7 +24079,7 @@
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Carl Jansson, Cajsa Björkén, Fredrik Wilde, Malin Löfgren, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Malin Löfgren, Fredrik Wilde, Cajsa Björkén, Carl Jansson</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
@@ -24180,7 +24180,7 @@
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Carl Jansson, Cajsa Björkén, Fredrik Wilde, Malin Löfgren, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Malin Löfgren, Fredrik Wilde, Cajsa Björkén, Carl Jansson</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
@@ -24281,7 +24281,7 @@
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Carl Jansson, Cajsa Björkén, Fredrik Wilde, Malin Löfgren, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Malin Löfgren, Fredrik Wilde, Cajsa Björkén, Carl Jansson</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -23569,7 +23569,7 @@
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Carl Jansson, Cajsa Björkén, Fredrik Wilde, Malin Löfgren, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Malin Löfgren, Fredrik Wilde, Cajsa Björkén, Carl Jansson</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
@@ -23877,7 +23877,7 @@
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Carl Jansson, Cajsa Björkén, Fredrik Wilde, Malin Löfgren, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Malin Löfgren, Fredrik Wilde, Cajsa Björkén, Carl Jansson</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
@@ -24387,7 +24387,7 @@
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Carl Jansson, Cajsa Björkén, Fredrik Wilde, Malin Löfgren, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Mattias Dalkvist, Malin Löfgren, Fredrik Wilde, Cajsa Björkén, Carl Jansson</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -24401,7 +24401,7 @@
         <v>127735630</v>
       </c>
       <c r="B231" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>127735621</v>
       </c>
       <c r="B232" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -24401,7 +24401,7 @@
         <v>127735630</v>
       </c>
       <c r="B231" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>127735621</v>
       </c>
       <c r="B232" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -24401,7 +24401,7 @@
         <v>127735630</v>
       </c>
       <c r="B231" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>127735621</v>
       </c>
       <c r="B232" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -24401,7 +24401,7 @@
         <v>127735630</v>
       </c>
       <c r="B231" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>127735621</v>
       </c>
       <c r="B232" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -24401,7 +24401,7 @@
         <v>127735630</v>
       </c>
       <c r="B231" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>127735621</v>
       </c>
       <c r="B232" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -24401,7 +24401,7 @@
         <v>127735630</v>
       </c>
       <c r="B231" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>127735621</v>
       </c>
       <c r="B232" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -24401,7 +24401,7 @@
         <v>127735630</v>
       </c>
       <c r="B231" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>127735621</v>
       </c>
       <c r="B232" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -24401,7 +24401,7 @@
         <v>127735630</v>
       </c>
       <c r="B231" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>127735621</v>
       </c>
       <c r="B232" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY232"/>
+  <dimension ref="A1:AY233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24608,6 +24608,111 @@
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>130088035</v>
+      </c>
+      <c r="B233" t="n">
+        <v>80061</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>385</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Liten aspgelélav</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Collema curtisporum</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Röjdtjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>678328</v>
+      </c>
+      <c r="R233" t="n">
+        <v>7105456</v>
+      </c>
+      <c r="S233" t="n">
+        <v>10</v>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT233" t="inlineStr"/>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30663-2025 artfynd.xlsx
+++ b/artfynd/A 30663-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY272"/>
+  <dimension ref="A1:AZ272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866144</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861048</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865945</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866143</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861120</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868575</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868577</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126815009</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865183</t>
         </is>
       </c>
     </row>
@@ -1709,6 +1759,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865772</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1810,6 +1865,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866162</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1907,6 +1967,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862271</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2015,6 +2080,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868601</t>
         </is>
       </c>
     </row>
@@ -2122,6 +2192,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130088035</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2220,6 +2295,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814986</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2321,6 +2401,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868627</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2422,6 +2507,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863394</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2523,6 +2613,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865286</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2624,6 +2719,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865287</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2730,6 +2830,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868592</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2831,6 +2936,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861054</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2930,6 +3040,11 @@
       <c r="AY23" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861056</t>
         </is>
       </c>
     </row>
@@ -3033,6 +3148,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865272</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3138,6 +3258,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865855</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3243,6 +3368,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865996</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3344,6 +3474,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868553</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3441,6 +3576,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862275</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3557,6 +3697,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865184</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3654,6 +3799,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862248</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3751,6 +3901,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126811329</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3852,6 +4007,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865383</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3953,6 +4113,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866163</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4054,6 +4219,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861053</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4151,6 +4321,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814997</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4248,6 +4423,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814998</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4345,6 +4525,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814999</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4442,6 +4627,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126815000</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4553,6 +4743,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126850977</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4664,6 +4859,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126851831</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4775,6 +4975,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126852084</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4886,6 +5091,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126853137</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4997,6 +5207,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126860442</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5108,6 +5323,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126860448</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5209,6 +5429,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861249</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5310,6 +5535,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861250</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5411,6 +5641,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861252</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5512,6 +5747,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861254</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5613,6 +5853,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861255</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5714,6 +5959,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861256</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5815,6 +6065,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861257</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5916,6 +6171,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861258</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6017,6 +6277,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861259</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6118,6 +6383,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861260</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6219,6 +6489,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861261</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6320,6 +6595,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861262</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6421,6 +6701,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861263</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6522,6 +6807,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861264</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6623,6 +6913,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861265</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6724,6 +7019,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861306</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6825,6 +7125,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861307</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6926,6 +7231,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861308</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7027,6 +7337,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861309</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7128,6 +7443,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861310</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7229,6 +7549,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861312</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7330,6 +7655,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861313</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7431,6 +7761,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861315</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7532,6 +7867,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861316</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7633,6 +7973,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861317</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7734,6 +8079,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861318</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7835,6 +8185,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861319</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7936,6 +8291,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861320</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8037,6 +8397,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861321</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8138,6 +8503,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861322</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8239,6 +8609,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861323</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8340,6 +8715,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861324</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8441,6 +8821,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861325</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8542,6 +8927,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861326</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8643,6 +9033,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861338</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8746,6 +9141,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862276</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8843,6 +9243,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862278</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8940,6 +9345,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862282</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9037,6 +9447,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862283</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9134,6 +9549,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862284</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9231,6 +9651,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862285</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9328,6 +9753,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862286</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9425,6 +9855,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862287</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9522,6 +9957,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862289</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9619,6 +10059,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862290</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9716,6 +10161,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862292</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9815,6 +10265,11 @@
       <c r="AY91" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863400</t>
         </is>
       </c>
     </row>
@@ -9922,6 +10377,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864769</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10031,6 +10491,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864836</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10147,6 +10612,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865181</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10263,6 +10733,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865182</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10379,6 +10854,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865185</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10480,6 +10960,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865292</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10581,6 +11066,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865298</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10682,6 +11172,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865299</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10783,6 +11278,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865300</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10884,6 +11384,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865309</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10985,6 +11490,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865310</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11086,6 +11596,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865314</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11187,6 +11702,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865315</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11288,6 +11808,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865316</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11389,6 +11914,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865317</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11490,6 +12020,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865452</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11596,6 +12131,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865453</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11695,6 +12235,11 @@
       <c r="AY109" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865454</t>
         </is>
       </c>
     </row>
@@ -11802,6 +12347,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865759</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11907,6 +12457,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865763</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12012,6 +12567,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865890</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12117,6 +12677,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865940</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12218,6 +12783,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866157</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12319,6 +12889,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866158</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12425,6 +13000,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868609</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12526,6 +13106,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868610</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12627,6 +13212,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868612</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12728,6 +13318,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865437</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12839,6 +13434,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126856160</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12937,6 +13537,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862302</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13051,6 +13656,11 @@
       <c r="AY122" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865187</t>
         </is>
       </c>
     </row>
@@ -13158,6 +13768,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865787</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13259,6 +13874,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865238</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13360,6 +13980,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866142</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13461,6 +14086,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868541</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13562,6 +14192,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868542</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13663,6 +14298,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861187</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13764,6 +14404,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861188</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13863,6 +14508,11 @@
       <c r="AY130" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861189</t>
         </is>
       </c>
     </row>
@@ -13970,6 +14620,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865757</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14071,6 +14726,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868594</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14172,6 +14832,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868596</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14273,6 +14938,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868597</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14374,6 +15044,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861046</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14471,6 +15146,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862243</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14572,6 +15252,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865242</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14673,6 +15358,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865421</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14774,6 +15464,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865428</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14875,6 +15570,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866146</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14976,6 +15676,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868547</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15077,6 +15782,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868548</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15178,6 +15888,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868549</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15279,6 +15994,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868550</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15380,6 +16100,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868551</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15481,6 +16206,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868552</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15582,6 +16312,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861100</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15683,6 +16418,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861101</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15784,6 +16524,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861103</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15885,6 +16630,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861104</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15986,6 +16736,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861105</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16100,6 +16855,11 @@
       <c r="AY152" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865178</t>
         </is>
       </c>
     </row>
@@ -16207,6 +16967,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865791</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16323,6 +17088,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865180</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16424,6 +17194,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868616</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16525,6 +17300,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868617</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16626,6 +17406,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868618</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16728,6 +17513,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16304727</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16825,6 +17615,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126811416</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16932,6 +17727,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126851438</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17043,6 +17843,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126860445</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17149,6 +17954,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861142</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17250,6 +18060,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861162</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17351,6 +18166,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861163</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17452,6 +18272,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861165</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17553,6 +18378,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861166</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17654,6 +18484,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861167</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17755,6 +18590,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861168</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17856,6 +18696,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861170</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17957,6 +18802,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861171</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18058,6 +18908,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861172</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18159,6 +19014,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861173</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18260,6 +19120,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861174</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18357,6 +19222,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862267</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18458,6 +19328,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864950</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18559,6 +19434,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865103</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18660,6 +19540,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865164</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18779,6 +19664,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865284</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18880,6 +19770,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865445</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18981,6 +19876,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868587</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19082,6 +19982,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868588</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19181,6 +20086,11 @@
       <c r="AY182" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868589</t>
         </is>
       </c>
     </row>
@@ -19288,6 +20198,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866024</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19389,6 +20304,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861079</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19490,6 +20410,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861080</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19591,6 +20516,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861081</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19692,6 +20622,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861082</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19791,6 +20726,11 @@
       <c r="AY188" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861083</t>
         </is>
       </c>
     </row>
@@ -19894,6 +20834,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865003</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19995,6 +20940,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865226</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20111,6 +21061,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865250</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20227,6 +21182,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865251</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20328,6 +21288,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868561</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20429,6 +21394,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868625</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20545,6 +21515,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865186</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20660,6 +21635,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861057</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20771,6 +21751,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861107</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20868,6 +21853,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862245</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20969,6 +21959,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863389</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21090,6 +22085,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866090</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21203,6 +22203,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868554</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21319,6 +22324,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126860452</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21426,6 +22436,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16304757</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21537,6 +22552,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126853157</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21634,6 +22654,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862249</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21735,6 +22760,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865243</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21836,6 +22866,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865246</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21933,6 +22968,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862274</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22039,6 +23079,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861122</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22153,6 +23198,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865296</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22268,6 +23318,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866426</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -22365,6 +23420,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126811407</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -22466,6 +23526,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861335</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22567,6 +23632,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861336</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22664,6 +23734,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862297</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22761,6 +23836,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862298</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22858,6 +23938,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862299</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22957,6 +24042,11 @@
       <c r="AY218" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866161</t>
         </is>
       </c>
     </row>
@@ -23065,6 +24155,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867967</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23170,6 +24265,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868614</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -23267,6 +24367,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126811397</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -23373,6 +24478,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814987</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -23479,6 +24589,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814989</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23585,6 +24700,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814991</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -23691,6 +24811,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814992</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23811,6 +24936,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126850880</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23926,6 +25056,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126851795</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24041,6 +25176,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126853557</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24162,6 +25302,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126853937</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -24277,6 +25422,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126860443</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -24392,6 +25542,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126860444</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -24507,6 +25662,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861190</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -24617,6 +25777,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861191</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -24727,6 +25892,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861196</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -24842,6 +26012,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861197</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -24957,6 +26132,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861198</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25067,6 +26247,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861201</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25177,6 +26362,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861202</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -25278,6 +26468,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863395</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -25379,6 +26574,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863396</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -25485,6 +26685,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865446</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -25595,6 +26800,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868598</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -25705,6 +26915,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868599</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -25811,6 +27026,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735621</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -25917,6 +27137,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735630</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26018,6 +27243,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861112</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26119,6 +27349,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861113</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -26225,6 +27460,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861090</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -26326,6 +27566,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865255</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -26427,6 +27672,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868591</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -26524,6 +27774,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126811343</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -26635,6 +27890,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126852438</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -26746,6 +28006,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126853218</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -26857,6 +28122,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126860446</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -26958,6 +28228,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861137</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -27059,6 +28334,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861138</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -27160,6 +28440,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861139</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -27257,6 +28542,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862264</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -27354,6 +28644,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862265</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -27455,6 +28750,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863392</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -27556,6 +28856,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865442</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -27655,6 +28960,11 @@
       <c r="AY262" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865443</t>
         </is>
       </c>
     </row>
@@ -27758,6 +29068,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865464</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -27863,6 +29178,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865754</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -27964,6 +29284,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866153</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -28065,6 +29390,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866154</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -28166,6 +29496,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126866155</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -28267,6 +29602,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868582</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -28371,6 +29711,11 @@
       <c r="AY269" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126861203</t>
         </is>
       </c>
     </row>
@@ -28478,6 +29823,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865776</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -28594,6 +29944,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865248</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -28695,8 +30050,286 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865431</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>